--- a/evac_by_zip/evac_by_zip_2026-08-13.xlsx
+++ b/evac_by_zip/evac_by_zip_2026-08-13.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="By ZIP Code" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Zone Detail" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By ZIP Code" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zone Detail" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -578,7 +578,7 @@
     <row r="2" ht="42" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Address counts estimated via area-weighted polygon intersection of OEM evac zones × Census ZCTA boundaries. Source: Oregon OEM Fire_Evacuation_Areas_Public + Census TIGERweb ZCTA. NOTE: 295 addresses (across 49 zones) could not be placed on a ZIP code this run and are NOT included in the totals below — see the summary rows at the bottom of this table and the Evacuation Map's 'Unmatched zones' layer for detail.</t>
+          <t>Address counts estimated via area-weighted polygon intersection of OEM evac zones × Census ZCTA boundaries. Source: Oregon OEM Fire_Evacuation_Areas_Public + Census TIGERweb ZCTA. NOTE: 295 addresses (across 0 zones) could not be placed on a ZIP code this run and are NOT included in the totals below — see the summary rows at the bottom of this table and the Evacuation Map's 'Unmatched zones' layer for detail.</t>
         </is>
       </c>
     </row>

--- a/evac_by_zip/evac_by_zip_2026-08-13.xlsx
+++ b/evac_by_zip/evac_by_zip_2026-08-13.xlsx
@@ -578,7 +578,7 @@
     <row r="2" ht="42" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Address counts estimated via area-weighted polygon intersection of OEM evac zones × Census ZCTA boundaries. Source: Oregon OEM Fire_Evacuation_Areas_Public + Census TIGERweb ZCTA. NOTE: 295 addresses (across 0 zones) could not be placed on a ZIP code this run and are NOT included in the totals below — see the summary rows at the bottom of this table and the Evacuation Map's 'Unmatched zones' layer for detail.</t>
+          <t>Address counts estimated via area-weighted polygon intersection of OEM evac zones × Census ZCTA boundaries. Source: Oregon OEM Fire_Evacuation_Areas_Public + Census TIGERweb ZCTA. NOTE: 291 addresses (across 0 zones) could not be placed on a ZIP code this run and are NOT included in the totals below — see the summary rows at the bottom of this table and the Evacuation Map's 'Unmatched zones' layer for detail.</t>
         </is>
       </c>
     </row>
@@ -1192,7 +1192,7 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>2</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         </is>
       </c>
       <c r="B23" s="11" t="n">
-        <v>1672</v>
+        <v>836</v>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         </is>
       </c>
       <c r="E23" s="10" t="n">
-        <v>1672</v>
+        <v>836</v>
       </c>
       <c r="F23" s="10" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="B36" s="11" t="n">
-        <v>1355</v>
+        <v>677</v>
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         </is>
       </c>
       <c r="E36" s="10" t="n">
-        <v>1355</v>
+        <v>677</v>
       </c>
       <c r="F36" s="10" t="inlineStr">
         <is>
@@ -2048,11 +2048,11 @@
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>97067</t>
+          <t>97711</t>
         </is>
       </c>
       <c r="B43" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         </is>
       </c>
       <c r="E43" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F43" s="10" t="inlineStr">
         <is>
@@ -2074,19 +2074,19 @@
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
-          <t>Clackamas</t>
+          <t>Jefferson</t>
         </is>
       </c>
       <c r="H43" s="12" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Rowe Creek Complex</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>97711</t>
+          <t>97067</t>
         </is>
       </c>
       <c r="B44" s="11" t="n">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
-          <t>Jefferson</t>
+          <t>Clackamas</t>
         </is>
       </c>
       <c r="H44" s="12" t="inlineStr">
         <is>
-          <t>Rowe Creek Complex</t>
+          <t>Grasshopper</t>
         </is>
       </c>
     </row>
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="B46" s="14" t="n">
-        <v>4922</v>
+        <v>3406</v>
       </c>
       <c r="C46" s="14" t="n">
         <v>2693</v>
@@ -2137,7 +2137,7 @@
         <v>1570</v>
       </c>
       <c r="E46" s="14" t="n">
-        <v>9185</v>
+        <v>7669</v>
       </c>
     </row>
     <row r="47">
@@ -2147,7 +2147,7 @@
         </is>
       </c>
       <c r="B47" s="16" t="n">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C47" s="16" t="n">
         <v>54</v>
@@ -2156,7 +2156,7 @@
         <v>59</v>
       </c>
       <c r="E47" s="16" t="n">
-        <v>295</v>
+        <v>291</v>
       </c>
     </row>
     <row r="48">
@@ -2166,7 +2166,7 @@
         </is>
       </c>
       <c r="B48" s="18" t="n">
-        <v>5104</v>
+        <v>3584</v>
       </c>
       <c r="C48" s="18" t="n">
         <v>2747</v>
@@ -2175,7 +2175,7 @@
         <v>1629</v>
       </c>
       <c r="E48" s="18" t="n">
-        <v>9480</v>
+        <v>7960</v>
       </c>
     </row>
   </sheetData>
@@ -2193,7 +2193,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G365"/>
+  <dimension ref="A1:G356"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8235,38 +8235,38 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="25" t="inlineStr">
-        <is>
-          <t>97041</t>
-        </is>
-      </c>
-      <c r="B174" s="26" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="C174" s="26" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
-        </is>
-      </c>
-      <c r="D174" s="26" t="inlineStr">
-        <is>
-          <t>Clackamas, Hood River</t>
-        </is>
-      </c>
-      <c r="E174" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F174" s="25" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G174" s="25" t="n">
-        <v>1</v>
+      <c r="A174" s="21" t="inlineStr">
+        <is>
+          <t>97639</t>
+        </is>
+      </c>
+      <c r="B174" s="22" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-1396</t>
+        </is>
+      </c>
+      <c r="C174" s="22" t="inlineStr">
+        <is>
+          <t>Wrights Spring</t>
+        </is>
+      </c>
+      <c r="D174" s="22" t="inlineStr">
+        <is>
+          <t>Klamath</t>
+        </is>
+      </c>
+      <c r="E174" s="21" t="inlineStr">
+        <is>
+          <t>Level 3 — GO NOW</t>
+        </is>
+      </c>
+      <c r="F174" s="21" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G174" s="21" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="175">
@@ -8277,7 +8277,7 @@
       </c>
       <c r="B175" s="22" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1396</t>
+          <t>US-OR-KLA-KLA-1426</t>
         </is>
       </c>
       <c r="C175" s="22" t="inlineStr">
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="G175" s="21" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
     </row>
     <row r="176">
@@ -8312,7 +8312,7 @@
       </c>
       <c r="B176" s="22" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1426</t>
+          <t>US-OR-KLA-KLA-1381-A</t>
         </is>
       </c>
       <c r="C176" s="22" t="inlineStr">
@@ -8332,11 +8332,11 @@
       </c>
       <c r="F176" s="21" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>54%</t>
         </is>
       </c>
       <c r="G176" s="21" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="177">
@@ -8347,7 +8347,7 @@
       </c>
       <c r="B177" s="22" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1381-A</t>
+          <t>US-OR-KLA-KLA-1566</t>
         </is>
       </c>
       <c r="C177" s="22" t="inlineStr">
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="G177" s="21" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="178">
@@ -8382,7 +8382,7 @@
       </c>
       <c r="B178" s="22" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1566</t>
+          <t>US-OR-KLA-KLA-1717</t>
         </is>
       </c>
       <c r="C178" s="22" t="inlineStr">
@@ -8402,11 +8402,11 @@
       </c>
       <c r="F178" s="21" t="inlineStr">
         <is>
-          <t>54%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="G178" s="21" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="179">
@@ -8417,7 +8417,7 @@
       </c>
       <c r="B179" s="22" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1717</t>
+          <t>US-OR-KLA-KLA-1572</t>
         </is>
       </c>
       <c r="C179" s="22" t="inlineStr">
@@ -8437,11 +8437,11 @@
       </c>
       <c r="F179" s="21" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="G179" s="21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="180">
@@ -8452,7 +8452,7 @@
       </c>
       <c r="B180" s="22" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1572</t>
+          <t>US-OR-KLA-KLA-1381-B</t>
         </is>
       </c>
       <c r="C180" s="22" t="inlineStr">
@@ -8472,7 +8472,7 @@
       </c>
       <c r="F180" s="21" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>47%</t>
         </is>
       </c>
       <c r="G180" s="21" t="n">
@@ -8487,7 +8487,7 @@
       </c>
       <c r="B181" s="22" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1381-B</t>
+          <t>US-OR-KLA-KLA-1718</t>
         </is>
       </c>
       <c r="C181" s="22" t="inlineStr">
@@ -8507,7 +8507,7 @@
       </c>
       <c r="F181" s="21" t="inlineStr">
         <is>
-          <t>47%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="G181" s="21" t="n">
@@ -8522,7 +8522,7 @@
       </c>
       <c r="B182" s="22" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1718</t>
+          <t>US-OR-KLA-FHZ-1582</t>
         </is>
       </c>
       <c r="C182" s="22" t="inlineStr">
@@ -8542,7 +8542,7 @@
       </c>
       <c r="F182" s="21" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G182" s="21" t="n">
@@ -8557,7 +8557,7 @@
       </c>
       <c r="B183" s="22" t="inlineStr">
         <is>
-          <t>US-OR-KLA-FHZ-1582</t>
+          <t>US-OR-KLA-KLA-1167</t>
         </is>
       </c>
       <c r="C183" s="22" t="inlineStr">
@@ -8585,38 +8585,38 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="21" t="inlineStr">
+      <c r="A184" s="23" t="inlineStr">
         <is>
           <t>97639</t>
         </is>
       </c>
-      <c r="B184" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1167</t>
-        </is>
-      </c>
-      <c r="C184" s="22" t="inlineStr">
+      <c r="B184" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-1386</t>
+        </is>
+      </c>
+      <c r="C184" s="24" t="inlineStr">
         <is>
           <t>Wrights Spring</t>
         </is>
       </c>
-      <c r="D184" s="22" t="inlineStr">
+      <c r="D184" s="24" t="inlineStr">
         <is>
           <t>Klamath</t>
         </is>
       </c>
-      <c r="E184" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F184" s="21" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G184" s="21" t="n">
-        <v>1</v>
+      <c r="E184" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F184" s="23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G184" s="23" t="n">
+        <v>63</v>
       </c>
     </row>
     <row r="185">
@@ -8627,7 +8627,7 @@
       </c>
       <c r="B185" s="24" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1386</t>
+          <t>US-OR-KLA-FHZ-1583</t>
         </is>
       </c>
       <c r="C185" s="24" t="inlineStr">
@@ -8647,11 +8647,11 @@
       </c>
       <c r="F185" s="23" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="G185" s="23" t="n">
-        <v>63</v>
+        <v>13</v>
       </c>
     </row>
     <row r="186">
@@ -8662,7 +8662,7 @@
       </c>
       <c r="B186" s="24" t="inlineStr">
         <is>
-          <t>US-OR-KLA-FHZ-1583</t>
+          <t>US-OR-KLA-KLA-1577</t>
         </is>
       </c>
       <c r="C186" s="24" t="inlineStr">
@@ -8682,11 +8682,11 @@
       </c>
       <c r="F186" s="23" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G186" s="23" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="187">
@@ -8697,7 +8697,7 @@
       </c>
       <c r="B187" s="24" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1577</t>
+          <t>US-OR-KLA-KLA-1431</t>
         </is>
       </c>
       <c r="C187" s="24" t="inlineStr">
@@ -8721,7 +8721,7 @@
         </is>
       </c>
       <c r="G187" s="23" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="188">
@@ -8732,7 +8732,7 @@
       </c>
       <c r="B188" s="24" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1431</t>
+          <t>US-OR-KLA-FHZ-1584-B</t>
         </is>
       </c>
       <c r="C188" s="24" t="inlineStr">
@@ -8752,7 +8752,7 @@
       </c>
       <c r="F188" s="23" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>99%</t>
         </is>
       </c>
       <c r="G188" s="23" t="n">
@@ -8760,37 +8760,37 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="23" t="inlineStr">
+      <c r="A189" s="25" t="inlineStr">
         <is>
           <t>97639</t>
         </is>
       </c>
-      <c r="B189" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-FHZ-1584-B</t>
-        </is>
-      </c>
-      <c r="C189" s="24" t="inlineStr">
+      <c r="B189" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-1371</t>
+        </is>
+      </c>
+      <c r="C189" s="26" t="inlineStr">
         <is>
           <t>Wrights Spring</t>
         </is>
       </c>
-      <c r="D189" s="24" t="inlineStr">
+      <c r="D189" s="26" t="inlineStr">
         <is>
           <t>Klamath</t>
         </is>
       </c>
-      <c r="E189" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F189" s="23" t="inlineStr">
-        <is>
-          <t>99%</t>
-        </is>
-      </c>
-      <c r="G189" s="23" t="n">
+      <c r="E189" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F189" s="25" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="G189" s="25" t="n">
         <v>2</v>
       </c>
     </row>
@@ -8802,7 +8802,7 @@
       </c>
       <c r="B190" s="26" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1371</t>
+          <t>US-OR-KLA-FHZ-1585</t>
         </is>
       </c>
       <c r="C190" s="26" t="inlineStr">
@@ -8822,11 +8822,11 @@
       </c>
       <c r="F190" s="25" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="G190" s="25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="191">
@@ -8837,7 +8837,7 @@
       </c>
       <c r="B191" s="26" t="inlineStr">
         <is>
-          <t>US-OR-KLA-FHZ-1585</t>
+          <t>US-OR-KLA-FHZ-1584-A</t>
         </is>
       </c>
       <c r="C191" s="26" t="inlineStr">
@@ -8857,7 +8857,7 @@
       </c>
       <c r="F191" s="25" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="G191" s="25" t="n">
@@ -8865,38 +8865,38 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="25" t="inlineStr">
-        <is>
-          <t>97639</t>
-        </is>
-      </c>
-      <c r="B192" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-FHZ-1584-A</t>
-        </is>
-      </c>
-      <c r="C192" s="26" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D192" s="26" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E192" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F192" s="25" t="inlineStr">
-        <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="G192" s="25" t="n">
-        <v>1</v>
+      <c r="A192" s="21" t="inlineStr">
+        <is>
+          <t>97058</t>
+        </is>
+      </c>
+      <c r="B192" s="22" t="inlineStr">
+        <is>
+          <t>WRR</t>
+        </is>
+      </c>
+      <c r="C192" s="22" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="D192" s="22" t="inlineStr">
+        <is>
+          <t>Wasco</t>
+        </is>
+      </c>
+      <c r="E192" s="21" t="inlineStr">
+        <is>
+          <t>Level 3 — GO NOW</t>
+        </is>
+      </c>
+      <c r="F192" s="21" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="G192" s="21" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="193">
@@ -8907,7 +8907,7 @@
       </c>
       <c r="B193" s="22" t="inlineStr">
         <is>
-          <t>WRR</t>
+          <t>WM</t>
         </is>
       </c>
       <c r="C193" s="22" t="inlineStr">
@@ -8927,46 +8927,46 @@
       </c>
       <c r="F193" s="21" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="G193" s="21" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="21" t="inlineStr">
+      <c r="A194" s="23" t="inlineStr">
         <is>
           <t>97058</t>
         </is>
       </c>
-      <c r="B194" s="22" t="inlineStr">
-        <is>
-          <t>WM</t>
-        </is>
-      </c>
-      <c r="C194" s="22" t="inlineStr">
+      <c r="B194" s="24" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="C194" s="24" t="inlineStr">
         <is>
           <t>Grasshopper</t>
         </is>
       </c>
-      <c r="D194" s="22" t="inlineStr">
+      <c r="D194" s="24" t="inlineStr">
         <is>
           <t>Wasco</t>
         </is>
       </c>
-      <c r="E194" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F194" s="21" t="inlineStr">
-        <is>
-          <t>2%</t>
-        </is>
-      </c>
-      <c r="G194" s="21" t="n">
-        <v>1</v>
+      <c r="E194" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F194" s="23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G194" s="23" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="195">
@@ -8977,7 +8977,7 @@
       </c>
       <c r="B195" s="24" t="inlineStr">
         <is>
-          <t>OR</t>
+          <t>PHR</t>
         </is>
       </c>
       <c r="C195" s="24" t="inlineStr">
@@ -9001,7 +9001,7 @@
         </is>
       </c>
       <c r="G195" s="23" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="196">
@@ -9012,7 +9012,7 @@
       </c>
       <c r="B196" s="24" t="inlineStr">
         <is>
-          <t>PHR</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="C196" s="24" t="inlineStr">
@@ -9032,46 +9032,46 @@
       </c>
       <c r="F196" s="23" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="G196" s="23" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="23" t="inlineStr">
+      <c r="A197" s="25" t="inlineStr">
         <is>
           <t>97058</t>
         </is>
       </c>
-      <c r="B197" s="24" t="inlineStr">
-        <is>
-          <t>CB</t>
-        </is>
-      </c>
-      <c r="C197" s="24" t="inlineStr">
+      <c r="B197" s="26" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="C197" s="26" t="inlineStr">
         <is>
           <t>Grasshopper</t>
         </is>
       </c>
-      <c r="D197" s="24" t="inlineStr">
+      <c r="D197" s="26" t="inlineStr">
         <is>
           <t>Wasco</t>
         </is>
       </c>
-      <c r="E197" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F197" s="23" t="inlineStr">
-        <is>
-          <t>64%</t>
-        </is>
-      </c>
-      <c r="G197" s="23" t="n">
-        <v>3</v>
+      <c r="E197" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F197" s="25" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G197" s="25" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="198">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="B198" s="26" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>UFM</t>
         </is>
       </c>
       <c r="C198" s="26" t="inlineStr">
@@ -9106,7 +9106,7 @@
         </is>
       </c>
       <c r="G198" s="25" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="199">
@@ -9117,7 +9117,7 @@
       </c>
       <c r="B199" s="26" t="inlineStr">
         <is>
-          <t>UFM</t>
+          <t>MCR</t>
         </is>
       </c>
       <c r="C199" s="26" t="inlineStr">
@@ -9137,46 +9137,46 @@
       </c>
       <c r="F199" s="25" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="G199" s="25" t="n">
-        <v>42</v>
+        <v>4</v>
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="25" t="inlineStr">
-        <is>
-          <t>97058</t>
-        </is>
-      </c>
-      <c r="B200" s="26" t="inlineStr">
-        <is>
-          <t>MCR</t>
-        </is>
-      </c>
-      <c r="C200" s="26" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
-        </is>
-      </c>
-      <c r="D200" s="26" t="inlineStr">
-        <is>
-          <t>Wasco</t>
-        </is>
-      </c>
-      <c r="E200" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F200" s="25" t="inlineStr">
-        <is>
-          <t>88%</t>
-        </is>
-      </c>
-      <c r="G200" s="25" t="n">
-        <v>4</v>
+      <c r="A200" s="21" t="inlineStr">
+        <is>
+          <t>97810</t>
+        </is>
+      </c>
+      <c r="B200" s="22" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-1406017-A</t>
+        </is>
+      </c>
+      <c r="C200" s="22" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D200" s="22" t="inlineStr">
+        <is>
+          <t>Umatilla</t>
+        </is>
+      </c>
+      <c r="E200" s="21" t="inlineStr">
+        <is>
+          <t>Level 3 — GO NOW</t>
+        </is>
+      </c>
+      <c r="F200" s="21" t="inlineStr">
+        <is>
+          <t>89%</t>
+        </is>
+      </c>
+      <c r="G200" s="21" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="201">
@@ -9187,7 +9187,7 @@
       </c>
       <c r="B201" s="22" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-1406017-A</t>
+          <t>US-OR-UMA-UMC-1406053-C</t>
         </is>
       </c>
       <c r="C201" s="22" t="inlineStr">
@@ -9207,11 +9207,11 @@
       </c>
       <c r="F201" s="21" t="inlineStr">
         <is>
-          <t>89%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G201" s="21" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
     </row>
     <row r="202">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="B202" s="22" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-1406053-C</t>
+          <t>US-OR-UMA-UMC-1406015-D</t>
         </is>
       </c>
       <c r="C202" s="22" t="inlineStr">
@@ -9246,7 +9246,7 @@
         </is>
       </c>
       <c r="G202" s="21" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="203">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="B203" s="22" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-1406015-D</t>
+          <t>US-OR-UMA-UMC-151-D</t>
         </is>
       </c>
       <c r="C203" s="22" t="inlineStr">
@@ -9277,11 +9277,11 @@
       </c>
       <c r="F203" s="21" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>53%</t>
         </is>
       </c>
       <c r="G203" s="21" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="204">
@@ -9292,7 +9292,7 @@
       </c>
       <c r="B204" s="22" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-151-D</t>
+          <t>US-OR-UMA-UMC-153</t>
         </is>
       </c>
       <c r="C204" s="22" t="inlineStr">
@@ -9312,7 +9312,7 @@
       </c>
       <c r="F204" s="21" t="inlineStr">
         <is>
-          <t>53%</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="G204" s="21" t="n">
@@ -9327,7 +9327,7 @@
       </c>
       <c r="B205" s="22" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-153</t>
+          <t>US-OR-UMA-UMC-1406015-A</t>
         </is>
       </c>
       <c r="C205" s="22" t="inlineStr">
@@ -9347,11 +9347,11 @@
       </c>
       <c r="F205" s="21" t="inlineStr">
         <is>
-          <t>64%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G205" s="21" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="206">
@@ -9362,7 +9362,7 @@
       </c>
       <c r="B206" s="22" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-1406015-A</t>
+          <t>US-OR-UMA-UMC-1406015-C</t>
         </is>
       </c>
       <c r="C206" s="22" t="inlineStr">
@@ -9386,7 +9386,7 @@
         </is>
       </c>
       <c r="G206" s="21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="207">
@@ -9397,7 +9397,7 @@
       </c>
       <c r="B207" s="22" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-1406015-C</t>
+          <t>US-OR-UMA-UMC-1406053-B</t>
         </is>
       </c>
       <c r="C207" s="22" t="inlineStr">
@@ -9421,7 +9421,7 @@
         </is>
       </c>
       <c r="G207" s="21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="208">
@@ -9432,7 +9432,7 @@
       </c>
       <c r="B208" s="22" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-1406053-B</t>
+          <t>US-OR-UMA-UMC-155-B</t>
         </is>
       </c>
       <c r="C208" s="22" t="inlineStr">
@@ -9452,7 +9452,7 @@
       </c>
       <c r="F208" s="21" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="G208" s="21" t="n">
@@ -9460,38 +9460,38 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="21" t="inlineStr">
+      <c r="A209" s="23" t="inlineStr">
         <is>
           <t>97810</t>
         </is>
       </c>
-      <c r="B209" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-155-B</t>
-        </is>
-      </c>
-      <c r="C209" s="22" t="inlineStr">
+      <c r="B209" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-215-E</t>
+        </is>
+      </c>
+      <c r="C209" s="24" t="inlineStr">
         <is>
           <t>No named fire</t>
         </is>
       </c>
-      <c r="D209" s="22" t="inlineStr">
+      <c r="D209" s="24" t="inlineStr">
         <is>
           <t>Umatilla</t>
         </is>
       </c>
-      <c r="E209" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F209" s="21" t="inlineStr">
-        <is>
-          <t>9%</t>
-        </is>
-      </c>
-      <c r="G209" s="21" t="n">
-        <v>1</v>
+      <c r="E209" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F209" s="23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G209" s="23" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="210">
@@ -9502,7 +9502,7 @@
       </c>
       <c r="B210" s="24" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-215-E</t>
+          <t>US-OR-UMA-UMC-215-D</t>
         </is>
       </c>
       <c r="C210" s="24" t="inlineStr">
@@ -9526,7 +9526,7 @@
         </is>
       </c>
       <c r="G210" s="23" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="211">
@@ -9537,7 +9537,7 @@
       </c>
       <c r="B211" s="24" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-215-D</t>
+          <t>US-OR-UMA-UMC-1406007-B</t>
         </is>
       </c>
       <c r="C211" s="24" t="inlineStr">
@@ -9557,11 +9557,11 @@
       </c>
       <c r="F211" s="23" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="G211" s="23" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="212">
@@ -9572,7 +9572,7 @@
       </c>
       <c r="B212" s="24" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-1406007-B</t>
+          <t>US-OR-UMA-UMC-149-B</t>
         </is>
       </c>
       <c r="C212" s="24" t="inlineStr">
@@ -9592,46 +9592,46 @@
       </c>
       <c r="F212" s="23" t="inlineStr">
         <is>
-          <t>89%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="G212" s="23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="23" t="inlineStr">
+      <c r="A213" s="25" t="inlineStr">
         <is>
           <t>97810</t>
         </is>
       </c>
-      <c r="B213" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-149-B</t>
-        </is>
-      </c>
-      <c r="C213" s="24" t="inlineStr">
+      <c r="B213" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-215-C</t>
+        </is>
+      </c>
+      <c r="C213" s="26" t="inlineStr">
         <is>
           <t>No named fire</t>
         </is>
       </c>
-      <c r="D213" s="24" t="inlineStr">
+      <c r="D213" s="26" t="inlineStr">
         <is>
           <t>Umatilla</t>
         </is>
       </c>
-      <c r="E213" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F213" s="23" t="inlineStr">
-        <is>
-          <t>67%</t>
-        </is>
-      </c>
-      <c r="G213" s="23" t="n">
-        <v>1</v>
+      <c r="E213" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F213" s="25" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G213" s="25" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="214">
@@ -9642,7 +9642,7 @@
       </c>
       <c r="B214" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-215-C</t>
+          <t>US-OR-UMA-UMC-215-F</t>
         </is>
       </c>
       <c r="C214" s="26" t="inlineStr">
@@ -9666,7 +9666,7 @@
         </is>
       </c>
       <c r="G214" s="25" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="215">
@@ -9677,7 +9677,7 @@
       </c>
       <c r="B215" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-215-F</t>
+          <t>US-OR-UMA-UMC-151-G</t>
         </is>
       </c>
       <c r="C215" s="26" t="inlineStr">
@@ -9697,46 +9697,46 @@
       </c>
       <c r="F215" s="25" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G215" s="25" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="25" t="inlineStr">
-        <is>
-          <t>97810</t>
-        </is>
-      </c>
-      <c r="B216" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-151-G</t>
-        </is>
-      </c>
-      <c r="C216" s="26" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D216" s="26" t="inlineStr">
-        <is>
-          <t>Umatilla</t>
-        </is>
-      </c>
-      <c r="E216" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F216" s="25" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G216" s="25" t="n">
-        <v>1</v>
+      <c r="A216" s="21" t="inlineStr">
+        <is>
+          <t>97621</t>
+        </is>
+      </c>
+      <c r="B216" s="22" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-1572</t>
+        </is>
+      </c>
+      <c r="C216" s="22" t="inlineStr">
+        <is>
+          <t>Wrights Spring</t>
+        </is>
+      </c>
+      <c r="D216" s="22" t="inlineStr">
+        <is>
+          <t>Klamath</t>
+        </is>
+      </c>
+      <c r="E216" s="21" t="inlineStr">
+        <is>
+          <t>Level 3 — GO NOW</t>
+        </is>
+      </c>
+      <c r="F216" s="21" t="inlineStr">
+        <is>
+          <t>31%</t>
+        </is>
+      </c>
+      <c r="G216" s="21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="217">
@@ -9747,7 +9747,7 @@
       </c>
       <c r="B217" s="22" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1572</t>
+          <t>US-OR-KLA-KLA-1566</t>
         </is>
       </c>
       <c r="C217" s="22" t="inlineStr">
@@ -9767,46 +9767,46 @@
       </c>
       <c r="F217" s="21" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="G217" s="21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="21" t="inlineStr">
+      <c r="A218" s="23" t="inlineStr">
         <is>
           <t>97621</t>
         </is>
       </c>
-      <c r="B218" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1566</t>
-        </is>
-      </c>
-      <c r="C218" s="22" t="inlineStr">
+      <c r="B218" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-1472</t>
+        </is>
+      </c>
+      <c r="C218" s="24" t="inlineStr">
         <is>
           <t>Wrights Spring</t>
         </is>
       </c>
-      <c r="D218" s="22" t="inlineStr">
+      <c r="D218" s="24" t="inlineStr">
         <is>
           <t>Klamath</t>
         </is>
       </c>
-      <c r="E218" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F218" s="21" t="inlineStr">
-        <is>
-          <t>9%</t>
-        </is>
-      </c>
-      <c r="G218" s="21" t="n">
-        <v>1</v>
+      <c r="E218" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F218" s="23" t="inlineStr">
+        <is>
+          <t>93%</t>
+        </is>
+      </c>
+      <c r="G218" s="23" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="219">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="B219" s="24" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1472</t>
+          <t>US-OR-KLA-FHZ-1584-B</t>
         </is>
       </c>
       <c r="C219" s="24" t="inlineStr">
@@ -9837,46 +9837,46 @@
       </c>
       <c r="F219" s="23" t="inlineStr">
         <is>
-          <t>93%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G219" s="23" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="23" t="inlineStr">
+      <c r="A220" s="25" t="inlineStr">
         <is>
           <t>97621</t>
         </is>
       </c>
-      <c r="B220" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-FHZ-1584-B</t>
-        </is>
-      </c>
-      <c r="C220" s="24" t="inlineStr">
+      <c r="B220" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-1471</t>
+        </is>
+      </c>
+      <c r="C220" s="26" t="inlineStr">
         <is>
           <t>Wrights Spring</t>
         </is>
       </c>
-      <c r="D220" s="24" t="inlineStr">
+      <c r="D220" s="26" t="inlineStr">
         <is>
           <t>Klamath</t>
         </is>
       </c>
-      <c r="E220" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F220" s="23" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G220" s="23" t="n">
-        <v>1</v>
+      <c r="E220" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F220" s="25" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G220" s="25" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="221">
@@ -9887,7 +9887,7 @@
       </c>
       <c r="B221" s="26" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1471</t>
+          <t>US-OR-KLA-KLA-1586</t>
         </is>
       </c>
       <c r="C221" s="26" t="inlineStr">
@@ -9911,7 +9911,7 @@
         </is>
       </c>
       <c r="G221" s="25" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="222">
@@ -9922,7 +9922,7 @@
       </c>
       <c r="B222" s="26" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1586</t>
+          <t>US-OR-KLA-FHZ-1584-A</t>
         </is>
       </c>
       <c r="C222" s="26" t="inlineStr">
@@ -9942,11 +9942,11 @@
       </c>
       <c r="F222" s="25" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>90%</t>
         </is>
       </c>
       <c r="G222" s="25" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="223">
@@ -9957,7 +9957,7 @@
       </c>
       <c r="B223" s="26" t="inlineStr">
         <is>
-          <t>US-OR-KLA-FHZ-1584-A</t>
+          <t>US-OR-KLA-KLA-1452</t>
         </is>
       </c>
       <c r="C223" s="26" t="inlineStr">
@@ -9977,11 +9977,11 @@
       </c>
       <c r="F223" s="25" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="G223" s="25" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="224">
@@ -9992,7 +9992,7 @@
       </c>
       <c r="B224" s="26" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1452</t>
+          <t>US-OR-KLA-FHZ-1585</t>
         </is>
       </c>
       <c r="C224" s="26" t="inlineStr">
@@ -10012,45 +10012,45 @@
       </c>
       <c r="F224" s="25" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="G224" s="25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="25" t="inlineStr">
-        <is>
-          <t>97621</t>
-        </is>
-      </c>
-      <c r="B225" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-FHZ-1585</t>
-        </is>
-      </c>
-      <c r="C225" s="26" t="inlineStr">
+      <c r="A225" s="21" t="inlineStr">
+        <is>
+          <t>97625</t>
+        </is>
+      </c>
+      <c r="B225" s="22" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-1713-B</t>
+        </is>
+      </c>
+      <c r="C225" s="22" t="inlineStr">
         <is>
           <t>Wrights Spring</t>
         </is>
       </c>
-      <c r="D225" s="26" t="inlineStr">
+      <c r="D225" s="22" t="inlineStr">
         <is>
           <t>Klamath</t>
         </is>
       </c>
-      <c r="E225" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F225" s="25" t="inlineStr">
-        <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="G225" s="25" t="n">
+      <c r="E225" s="21" t="inlineStr">
+        <is>
+          <t>Level 3 — GO NOW</t>
+        </is>
+      </c>
+      <c r="F225" s="21" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="G225" s="21" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10062,7 +10062,7 @@
       </c>
       <c r="B226" s="22" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1713-B</t>
+          <t>US-OR-KLA-KLA-1713-A</t>
         </is>
       </c>
       <c r="C226" s="22" t="inlineStr">
@@ -10082,7 +10082,7 @@
       </c>
       <c r="F226" s="21" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G226" s="21" t="n">
@@ -10090,38 +10090,38 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="21" t="inlineStr">
+      <c r="A227" s="23" t="inlineStr">
         <is>
           <t>97625</t>
         </is>
       </c>
-      <c r="B227" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1713-A</t>
-        </is>
-      </c>
-      <c r="C227" s="22" t="inlineStr">
+      <c r="B227" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-1707</t>
+        </is>
+      </c>
+      <c r="C227" s="24" t="inlineStr">
         <is>
           <t>Wrights Spring</t>
         </is>
       </c>
-      <c r="D227" s="22" t="inlineStr">
+      <c r="D227" s="24" t="inlineStr">
         <is>
           <t>Klamath</t>
         </is>
       </c>
-      <c r="E227" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F227" s="21" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G227" s="21" t="n">
-        <v>1</v>
+      <c r="E227" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F227" s="23" t="inlineStr">
+        <is>
+          <t>84%</t>
+        </is>
+      </c>
+      <c r="G227" s="23" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="228">
@@ -10132,7 +10132,7 @@
       </c>
       <c r="B228" s="24" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1707</t>
+          <t>US-OR-KLA-KLA-1941</t>
         </is>
       </c>
       <c r="C228" s="24" t="inlineStr">
@@ -10152,11 +10152,11 @@
       </c>
       <c r="F228" s="23" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="G228" s="23" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
     </row>
     <row r="229">
@@ -10167,7 +10167,7 @@
       </c>
       <c r="B229" s="24" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1941</t>
+          <t>US-OR-KLA-KLA-1956</t>
         </is>
       </c>
       <c r="C229" s="24" t="inlineStr">
@@ -10187,46 +10187,46 @@
       </c>
       <c r="F229" s="23" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G229" s="23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="23" t="inlineStr">
+      <c r="A230" s="25" t="inlineStr">
         <is>
           <t>97625</t>
         </is>
       </c>
-      <c r="B230" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1956</t>
-        </is>
-      </c>
-      <c r="C230" s="24" t="inlineStr">
+      <c r="B230" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-2261</t>
+        </is>
+      </c>
+      <c r="C230" s="26" t="inlineStr">
         <is>
           <t>Wrights Spring</t>
         </is>
       </c>
-      <c r="D230" s="24" t="inlineStr">
+      <c r="D230" s="26" t="inlineStr">
         <is>
           <t>Klamath</t>
         </is>
       </c>
-      <c r="E230" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F230" s="23" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G230" s="23" t="n">
-        <v>1</v>
+      <c r="E230" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F230" s="25" t="inlineStr">
+        <is>
+          <t>31%</t>
+        </is>
+      </c>
+      <c r="G230" s="25" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="231">
@@ -10237,7 +10237,7 @@
       </c>
       <c r="B231" s="26" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-2261</t>
+          <t>US-OR-KLA-KLA-1946</t>
         </is>
       </c>
       <c r="C231" s="26" t="inlineStr">
@@ -10257,11 +10257,11 @@
       </c>
       <c r="F231" s="25" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="G231" s="25" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="232">
@@ -10272,7 +10272,7 @@
       </c>
       <c r="B232" s="26" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1946</t>
+          <t>US-OR-KLA-KLA-1701</t>
         </is>
       </c>
       <c r="C232" s="26" t="inlineStr">
@@ -10292,11 +10292,11 @@
       </c>
       <c r="F232" s="25" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G232" s="25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="233">
@@ -10307,7 +10307,7 @@
       </c>
       <c r="B233" s="26" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1701</t>
+          <t>US-OR-KLA-KLA-1361</t>
         </is>
       </c>
       <c r="C233" s="26" t="inlineStr">
@@ -10335,37 +10335,37 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="25" t="inlineStr">
-        <is>
-          <t>97625</t>
-        </is>
-      </c>
-      <c r="B234" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1361</t>
-        </is>
-      </c>
-      <c r="C234" s="26" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D234" s="26" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E234" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F234" s="25" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G234" s="25" t="n">
+      <c r="A234" s="21" t="inlineStr">
+        <is>
+          <t>97907</t>
+        </is>
+      </c>
+      <c r="B234" s="22" t="inlineStr">
+        <is>
+          <t>US-OR-BAK-BAB-1416-A</t>
+        </is>
+      </c>
+      <c r="C234" s="22" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D234" s="22" t="inlineStr">
+        <is>
+          <t>Baker</t>
+        </is>
+      </c>
+      <c r="E234" s="21" t="inlineStr">
+        <is>
+          <t>Level 3 — GO NOW</t>
+        </is>
+      </c>
+      <c r="F234" s="21" t="inlineStr">
+        <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="G234" s="21" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10377,7 +10377,7 @@
       </c>
       <c r="B235" s="22" t="inlineStr">
         <is>
-          <t>US-OR-BAK-BAB-1416-A</t>
+          <t>US-OR-BAK-RCH-572</t>
         </is>
       </c>
       <c r="C235" s="22" t="inlineStr">
@@ -10397,7 +10397,7 @@
       </c>
       <c r="F235" s="21" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>26%</t>
         </is>
       </c>
       <c r="G235" s="21" t="n">
@@ -10405,38 +10405,38 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="21" t="inlineStr">
+      <c r="A236" s="23" t="inlineStr">
         <is>
           <t>97907</t>
         </is>
       </c>
-      <c r="B236" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-BAK-RCH-572</t>
-        </is>
-      </c>
-      <c r="C236" s="22" t="inlineStr">
+      <c r="B236" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-BAK-BAB-1410-A</t>
+        </is>
+      </c>
+      <c r="C236" s="24" t="inlineStr">
         <is>
           <t>No named fire</t>
         </is>
       </c>
-      <c r="D236" s="22" t="inlineStr">
+      <c r="D236" s="24" t="inlineStr">
         <is>
           <t>Baker</t>
         </is>
       </c>
-      <c r="E236" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F236" s="21" t="inlineStr">
-        <is>
-          <t>26%</t>
-        </is>
-      </c>
-      <c r="G236" s="21" t="n">
-        <v>1</v>
+      <c r="E236" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F236" s="23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G236" s="23" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="237">
@@ -10447,7 +10447,7 @@
       </c>
       <c r="B237" s="24" t="inlineStr">
         <is>
-          <t>US-OR-BAK-BAB-1410-A</t>
+          <t>US-OR-BAK-BAB-1412-A</t>
         </is>
       </c>
       <c r="C237" s="24" t="inlineStr">
@@ -10467,11 +10467,11 @@
       </c>
       <c r="F237" s="23" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="G237" s="23" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
     </row>
     <row r="238">
@@ -10482,7 +10482,7 @@
       </c>
       <c r="B238" s="24" t="inlineStr">
         <is>
-          <t>US-OR-BAK-BAB-1412-A</t>
+          <t>US-OR-BAK-BAB-1414-A</t>
         </is>
       </c>
       <c r="C238" s="24" t="inlineStr">
@@ -10502,11 +10502,11 @@
       </c>
       <c r="F238" s="23" t="inlineStr">
         <is>
-          <t>89%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="G238" s="23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="239">
@@ -10517,7 +10517,7 @@
       </c>
       <c r="B239" s="24" t="inlineStr">
         <is>
-          <t>US-OR-BAK-BAB-1414-A</t>
+          <t>US-OR-BAK-BAB-1408-A</t>
         </is>
       </c>
       <c r="C239" s="24" t="inlineStr">
@@ -10537,11 +10537,11 @@
       </c>
       <c r="F239" s="23" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G239" s="23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="240">
@@ -10552,7 +10552,7 @@
       </c>
       <c r="B240" s="24" t="inlineStr">
         <is>
-          <t>US-OR-BAK-BAB-1408-A</t>
+          <t>US-OR-BAK-RCH-570</t>
         </is>
       </c>
       <c r="C240" s="24" t="inlineStr">
@@ -10572,46 +10572,46 @@
       </c>
       <c r="F240" s="23" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="G240" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="23" t="inlineStr">
+      <c r="A241" s="25" t="inlineStr">
         <is>
           <t>97907</t>
         </is>
       </c>
-      <c r="B241" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-BAK-RCH-570</t>
-        </is>
-      </c>
-      <c r="C241" s="24" t="inlineStr">
+      <c r="B241" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-BAK-HUN-317</t>
+        </is>
+      </c>
+      <c r="C241" s="26" t="inlineStr">
         <is>
           <t>No named fire</t>
         </is>
       </c>
-      <c r="D241" s="24" t="inlineStr">
+      <c r="D241" s="26" t="inlineStr">
         <is>
           <t>Baker</t>
         </is>
       </c>
-      <c r="E241" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F241" s="23" t="inlineStr">
-        <is>
-          <t>1%</t>
-        </is>
-      </c>
-      <c r="G241" s="23" t="n">
-        <v>1</v>
+      <c r="E241" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F241" s="25" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G241" s="25" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="242">
@@ -10622,7 +10622,7 @@
       </c>
       <c r="B242" s="26" t="inlineStr">
         <is>
-          <t>US-OR-BAK-HUN-317</t>
+          <t>US-OR-BAK-HUN-315</t>
         </is>
       </c>
       <c r="C242" s="26" t="inlineStr">
@@ -10657,7 +10657,7 @@
       </c>
       <c r="B243" s="26" t="inlineStr">
         <is>
-          <t>US-OR-BAK-HUN-315</t>
+          <t>US-OR-BAK-HUN-319</t>
         </is>
       </c>
       <c r="C243" s="26" t="inlineStr">
@@ -10681,7 +10681,7 @@
         </is>
       </c>
       <c r="G243" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="244">
@@ -10692,7 +10692,7 @@
       </c>
       <c r="B244" s="26" t="inlineStr">
         <is>
-          <t>US-OR-BAK-HUN-319</t>
+          <t>US-OR-BAK-HUN-321</t>
         </is>
       </c>
       <c r="C244" s="26" t="inlineStr">
@@ -10727,7 +10727,7 @@
       </c>
       <c r="B245" s="26" t="inlineStr">
         <is>
-          <t>US-OR-BAK-HUN-321</t>
+          <t>US-OR-BAK-BAB-1528</t>
         </is>
       </c>
       <c r="C245" s="26" t="inlineStr">
@@ -10751,42 +10751,42 @@
         </is>
       </c>
       <c r="G245" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="25" t="inlineStr">
-        <is>
-          <t>97907</t>
-        </is>
-      </c>
-      <c r="B246" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-BAK-BAB-1528</t>
-        </is>
-      </c>
-      <c r="C246" s="26" t="inlineStr">
+      <c r="A246" s="21" t="inlineStr">
+        <is>
+          <t>97827</t>
+        </is>
+      </c>
+      <c r="B246" s="22" t="inlineStr">
+        <is>
+          <t>US-OR-UNI-UCO-140618N</t>
+        </is>
+      </c>
+      <c r="C246" s="22" t="inlineStr">
         <is>
           <t>No named fire</t>
         </is>
       </c>
-      <c r="D246" s="26" t="inlineStr">
-        <is>
-          <t>Baker</t>
-        </is>
-      </c>
-      <c r="E246" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F246" s="25" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G246" s="25" t="n">
-        <v>2</v>
+      <c r="D246" s="22" t="inlineStr">
+        <is>
+          <t>Umatilla, Union</t>
+        </is>
+      </c>
+      <c r="E246" s="21" t="inlineStr">
+        <is>
+          <t>Level 3 — GO NOW</t>
+        </is>
+      </c>
+      <c r="F246" s="21" t="inlineStr">
+        <is>
+          <t>68%</t>
+        </is>
+      </c>
+      <c r="G246" s="21" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="247">
@@ -10797,7 +10797,7 @@
       </c>
       <c r="B247" s="22" t="inlineStr">
         <is>
-          <t>US-OR-UNI-UCO-140618N</t>
+          <t>US-OR-UNI-UCO-140624N-B</t>
         </is>
       </c>
       <c r="C247" s="22" t="inlineStr">
@@ -10817,11 +10817,11 @@
       </c>
       <c r="F247" s="21" t="inlineStr">
         <is>
-          <t>68%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="G247" s="21" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="248">
@@ -10832,7 +10832,7 @@
       </c>
       <c r="B248" s="22" t="inlineStr">
         <is>
-          <t>US-OR-UNI-UCO-140624N-B</t>
+          <t>US-OR-UNI-UCO-140624S</t>
         </is>
       </c>
       <c r="C248" s="22" t="inlineStr">
@@ -10852,11 +10852,11 @@
       </c>
       <c r="F248" s="21" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>46%</t>
         </is>
       </c>
       <c r="G248" s="21" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="249">
@@ -10867,7 +10867,7 @@
       </c>
       <c r="B249" s="22" t="inlineStr">
         <is>
-          <t>US-OR-UNI-UCO-140624S</t>
+          <t>US-OR-UMA-UMC-1406030-A</t>
         </is>
       </c>
       <c r="C249" s="22" t="inlineStr">
@@ -10887,7 +10887,7 @@
       </c>
       <c r="F249" s="21" t="inlineStr">
         <is>
-          <t>46%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G249" s="21" t="n">
@@ -10902,7 +10902,7 @@
       </c>
       <c r="B250" s="22" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-1406030-A</t>
+          <t>US-OR-UMA-UMC-1406024A</t>
         </is>
       </c>
       <c r="C250" s="22" t="inlineStr">
@@ -10930,37 +10930,37 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="21" t="inlineStr">
+      <c r="A251" s="25" t="inlineStr">
         <is>
           <t>97827</t>
         </is>
       </c>
-      <c r="B251" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-1406024A</t>
-        </is>
-      </c>
-      <c r="C251" s="22" t="inlineStr">
+      <c r="B251" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-UNI-UCO-1497</t>
+        </is>
+      </c>
+      <c r="C251" s="26" t="inlineStr">
         <is>
           <t>No named fire</t>
         </is>
       </c>
-      <c r="D251" s="22" t="inlineStr">
+      <c r="D251" s="26" t="inlineStr">
         <is>
           <t>Umatilla, Union</t>
         </is>
       </c>
-      <c r="E251" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F251" s="21" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G251" s="21" t="n">
+      <c r="E251" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F251" s="25" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="G251" s="25" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10972,7 +10972,7 @@
       </c>
       <c r="B252" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UNI-UCO-1497</t>
+          <t>US-OR-UNI-UCO-1505</t>
         </is>
       </c>
       <c r="C252" s="26" t="inlineStr">
@@ -10992,7 +10992,7 @@
       </c>
       <c r="F252" s="25" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>53%</t>
         </is>
       </c>
       <c r="G252" s="25" t="n">
@@ -11007,7 +11007,7 @@
       </c>
       <c r="B253" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UNI-UCO-1505</t>
+          <t>US-OR-UNI-UCO-1513</t>
         </is>
       </c>
       <c r="C253" s="26" t="inlineStr">
@@ -11027,7 +11027,7 @@
       </c>
       <c r="F253" s="25" t="inlineStr">
         <is>
-          <t>53%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="G253" s="25" t="n">
@@ -11042,7 +11042,7 @@
       </c>
       <c r="B254" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UNI-UCO-1513</t>
+          <t>US-OR-UNI-UCO-1495</t>
         </is>
       </c>
       <c r="C254" s="26" t="inlineStr">
@@ -11062,7 +11062,7 @@
       </c>
       <c r="F254" s="25" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G254" s="25" t="n">
@@ -11070,38 +11070,38 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="25" t="inlineStr">
-        <is>
-          <t>97827</t>
-        </is>
-      </c>
-      <c r="B255" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-UNI-UCO-1495</t>
-        </is>
-      </c>
-      <c r="C255" s="26" t="inlineStr">
+      <c r="A255" s="21" t="inlineStr">
+        <is>
+          <t>97905</t>
+        </is>
+      </c>
+      <c r="B255" s="22" t="inlineStr">
+        <is>
+          <t>US-OR-BAK-BAB-1404-A</t>
+        </is>
+      </c>
+      <c r="C255" s="22" t="inlineStr">
         <is>
           <t>No named fire</t>
         </is>
       </c>
-      <c r="D255" s="26" t="inlineStr">
-        <is>
-          <t>Umatilla, Union</t>
-        </is>
-      </c>
-      <c r="E255" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F255" s="25" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G255" s="25" t="n">
-        <v>1</v>
+      <c r="D255" s="22" t="inlineStr">
+        <is>
+          <t>Baker</t>
+        </is>
+      </c>
+      <c r="E255" s="21" t="inlineStr">
+        <is>
+          <t>Level 3 — GO NOW</t>
+        </is>
+      </c>
+      <c r="F255" s="21" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G255" s="21" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="256">
@@ -11112,7 +11112,7 @@
       </c>
       <c r="B256" s="22" t="inlineStr">
         <is>
-          <t>US-OR-BAK-BAB-1404-A</t>
+          <t>US-OR-BAK-BAB-1406-B</t>
         </is>
       </c>
       <c r="C256" s="22" t="inlineStr">
@@ -11136,7 +11136,7 @@
         </is>
       </c>
       <c r="G256" s="21" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="257">
@@ -11147,7 +11147,7 @@
       </c>
       <c r="B257" s="22" t="inlineStr">
         <is>
-          <t>US-OR-BAK-BAB-1406-B</t>
+          <t>US-OR-BAK-BAB-1416-A</t>
         </is>
       </c>
       <c r="C257" s="22" t="inlineStr">
@@ -11167,11 +11167,11 @@
       </c>
       <c r="F257" s="21" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="G257" s="21" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="258">
@@ -11182,7 +11182,7 @@
       </c>
       <c r="B258" s="22" t="inlineStr">
         <is>
-          <t>US-OR-BAK-BAB-1416-A</t>
+          <t>US-OR-BAK-BAB-1418-A</t>
         </is>
       </c>
       <c r="C258" s="22" t="inlineStr">
@@ -11202,46 +11202,46 @@
       </c>
       <c r="F258" s="21" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G258" s="21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="21" t="inlineStr">
+      <c r="A259" s="23" t="inlineStr">
         <is>
           <t>97905</t>
         </is>
       </c>
-      <c r="B259" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-BAK-BAB-1418-A</t>
-        </is>
-      </c>
-      <c r="C259" s="22" t="inlineStr">
+      <c r="B259" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-BAK-BAB-1414-A</t>
+        </is>
+      </c>
+      <c r="C259" s="24" t="inlineStr">
         <is>
           <t>No named fire</t>
         </is>
       </c>
-      <c r="D259" s="22" t="inlineStr">
+      <c r="D259" s="24" t="inlineStr">
         <is>
           <t>Baker</t>
         </is>
       </c>
-      <c r="E259" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F259" s="21" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G259" s="21" t="n">
-        <v>4</v>
+      <c r="E259" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F259" s="23" t="inlineStr">
+        <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="G259" s="23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="260">
@@ -11252,7 +11252,7 @@
       </c>
       <c r="B260" s="24" t="inlineStr">
         <is>
-          <t>US-OR-BAK-BAB-1414-A</t>
+          <t>US-OR-BAK-BAB-1412-A</t>
         </is>
       </c>
       <c r="C260" s="24" t="inlineStr">
@@ -11272,7 +11272,7 @@
       </c>
       <c r="F260" s="23" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>11%</t>
         </is>
       </c>
       <c r="G260" s="23" t="n">
@@ -11280,38 +11280,38 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="23" t="inlineStr">
-        <is>
-          <t>97905</t>
-        </is>
-      </c>
-      <c r="B261" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-BAK-BAB-1412-A</t>
-        </is>
-      </c>
-      <c r="C261" s="24" t="inlineStr">
+      <c r="A261" s="21" t="inlineStr">
+        <is>
+          <t>97862</t>
+        </is>
+      </c>
+      <c r="B261" s="22" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-123-B</t>
+        </is>
+      </c>
+      <c r="C261" s="22" t="inlineStr">
         <is>
           <t>No named fire</t>
         </is>
       </c>
-      <c r="D261" s="24" t="inlineStr">
-        <is>
-          <t>Baker</t>
-        </is>
-      </c>
-      <c r="E261" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F261" s="23" t="inlineStr">
-        <is>
-          <t>11%</t>
-        </is>
-      </c>
-      <c r="G261" s="23" t="n">
-        <v>1</v>
+      <c r="D261" s="22" t="inlineStr">
+        <is>
+          <t>Umatilla</t>
+        </is>
+      </c>
+      <c r="E261" s="21" t="inlineStr">
+        <is>
+          <t>Level 3 — GO NOW</t>
+        </is>
+      </c>
+      <c r="F261" s="21" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="G261" s="21" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="262">
@@ -11322,7 +11322,7 @@
       </c>
       <c r="B262" s="22" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-123-B</t>
+          <t>US-OR-UMA-UMC-121-B</t>
         </is>
       </c>
       <c r="C262" s="22" t="inlineStr">
@@ -11342,232 +11342,232 @@
       </c>
       <c r="F262" s="21" t="inlineStr">
         <is>
-          <t>28%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G262" s="21" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="21" t="inlineStr">
+      <c r="A263" s="23" t="inlineStr">
         <is>
           <t>97862</t>
         </is>
       </c>
-      <c r="B263" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-121-B</t>
-        </is>
-      </c>
-      <c r="C263" s="22" t="inlineStr">
+      <c r="B263" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-1406025-B</t>
+        </is>
+      </c>
+      <c r="C263" s="24" t="inlineStr">
         <is>
           <t>No named fire</t>
         </is>
       </c>
-      <c r="D263" s="22" t="inlineStr">
+      <c r="D263" s="24" t="inlineStr">
         <is>
           <t>Umatilla</t>
         </is>
       </c>
-      <c r="E263" s="21" t="inlineStr">
+      <c r="E263" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F263" s="23" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="G263" s="23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="21" t="inlineStr">
+        <is>
+          <t>97023</t>
+        </is>
+      </c>
+      <c r="B264" s="22" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="C264" s="22" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D264" s="22" t="inlineStr">
+        <is>
+          <t>Clackamas</t>
+        </is>
+      </c>
+      <c r="E264" s="21" t="inlineStr">
         <is>
           <t>Level 3 — GO NOW</t>
         </is>
       </c>
-      <c r="F263" s="21" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G263" s="21" t="n">
+      <c r="F264" s="21" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G264" s="21" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="25" t="inlineStr">
+        <is>
+          <t>97023</t>
+        </is>
+      </c>
+      <c r="B265" s="26" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="C265" s="26" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D265" s="26" t="inlineStr">
+        <is>
+          <t>Clackamas</t>
+        </is>
+      </c>
+      <c r="E265" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F265" s="25" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G265" s="25" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="264">
-      <c r="A264" s="23" t="inlineStr">
-        <is>
-          <t>97862</t>
-        </is>
-      </c>
-      <c r="B264" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-1406025-B</t>
-        </is>
-      </c>
-      <c r="C264" s="24" t="inlineStr">
+    <row r="266">
+      <c r="A266" s="21" t="inlineStr">
+        <is>
+          <t>97870</t>
+        </is>
+      </c>
+      <c r="B266" s="22" t="inlineStr">
+        <is>
+          <t>US-OR-BAK-RCH-572</t>
+        </is>
+      </c>
+      <c r="C266" s="22" t="inlineStr">
         <is>
           <t>No named fire</t>
         </is>
       </c>
-      <c r="D264" s="24" t="inlineStr">
-        <is>
-          <t>Umatilla</t>
-        </is>
-      </c>
-      <c r="E264" s="23" t="inlineStr">
+      <c r="D266" s="22" t="inlineStr">
+        <is>
+          <t>Baker</t>
+        </is>
+      </c>
+      <c r="E266" s="21" t="inlineStr">
+        <is>
+          <t>Level 3 — GO NOW</t>
+        </is>
+      </c>
+      <c r="F266" s="21" t="inlineStr">
+        <is>
+          <t>72%</t>
+        </is>
+      </c>
+      <c r="G266" s="21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="21" t="inlineStr">
+        <is>
+          <t>97870</t>
+        </is>
+      </c>
+      <c r="B267" s="22" t="inlineStr">
+        <is>
+          <t>US-OR-BAK-BAB-1313</t>
+        </is>
+      </c>
+      <c r="C267" s="22" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D267" s="22" t="inlineStr">
+        <is>
+          <t>Baker</t>
+        </is>
+      </c>
+      <c r="E267" s="21" t="inlineStr">
+        <is>
+          <t>Level 3 — GO NOW</t>
+        </is>
+      </c>
+      <c r="F267" s="21" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="G267" s="21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="23" t="inlineStr">
+        <is>
+          <t>97870</t>
+        </is>
+      </c>
+      <c r="B268" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-BAK-RCH-570</t>
+        </is>
+      </c>
+      <c r="C268" s="24" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D268" s="24" t="inlineStr">
+        <is>
+          <t>Baker</t>
+        </is>
+      </c>
+      <c r="E268" s="23" t="inlineStr">
         <is>
           <t>Level 2 — GET SET</t>
         </is>
       </c>
-      <c r="F264" s="23" t="inlineStr">
-        <is>
-          <t>2%</t>
-        </is>
-      </c>
-      <c r="G264" s="23" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" s="21" t="inlineStr">
-        <is>
-          <t>97023</t>
-        </is>
-      </c>
-      <c r="B265" s="22" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="C265" s="22" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D265" s="22" t="inlineStr">
-        <is>
-          <t>Clackamas</t>
-        </is>
-      </c>
-      <c r="E265" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F265" s="21" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G265" s="21" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" s="25" t="inlineStr">
-        <is>
-          <t>97023</t>
-        </is>
-      </c>
-      <c r="B266" s="26" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="C266" s="26" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D266" s="26" t="inlineStr">
-        <is>
-          <t>Clackamas</t>
-        </is>
-      </c>
-      <c r="E266" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F266" s="25" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G266" s="25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" s="25" t="inlineStr">
-        <is>
-          <t>97023</t>
-        </is>
-      </c>
-      <c r="B267" s="26" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="C267" s="26" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D267" s="26" t="inlineStr">
-        <is>
-          <t>Clackamas</t>
-        </is>
-      </c>
-      <c r="E267" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F267" s="25" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G267" s="25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" s="21" t="inlineStr">
-        <is>
-          <t>97870</t>
-        </is>
-      </c>
-      <c r="B268" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-BAK-RCH-572</t>
-        </is>
-      </c>
-      <c r="C268" s="22" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D268" s="22" t="inlineStr">
-        <is>
-          <t>Baker</t>
-        </is>
-      </c>
-      <c r="E268" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F268" s="21" t="inlineStr">
-        <is>
-          <t>72%</t>
-        </is>
-      </c>
-      <c r="G268" s="21" t="n">
+      <c r="F268" s="23" t="inlineStr">
+        <is>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="G268" s="23" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="21" t="inlineStr">
         <is>
-          <t>97870</t>
+          <t>97859</t>
         </is>
       </c>
       <c r="B269" s="22" t="inlineStr">
         <is>
-          <t>US-OR-BAK-BAB-1313</t>
+          <t>US-OR-UMA-UMC-1406015-D</t>
         </is>
       </c>
       <c r="C269" s="22" t="inlineStr">
@@ -11577,7 +11577,7 @@
       </c>
       <c r="D269" s="22" t="inlineStr">
         <is>
-          <t>Baker</t>
+          <t>Umatilla</t>
         </is>
       </c>
       <c r="E269" s="21" t="inlineStr">
@@ -11587,7 +11587,7 @@
       </c>
       <c r="F269" s="21" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G269" s="21" t="n">
@@ -11597,12 +11597,12 @@
     <row r="270">
       <c r="A270" s="23" t="inlineStr">
         <is>
-          <t>97870</t>
+          <t>97859</t>
         </is>
       </c>
       <c r="B270" s="24" t="inlineStr">
         <is>
-          <t>US-OR-BAK-RCH-570</t>
+          <t>US-OR-UMA-UMC-1406007-B</t>
         </is>
       </c>
       <c r="C270" s="24" t="inlineStr">
@@ -11612,7 +11612,7 @@
       </c>
       <c r="D270" s="24" t="inlineStr">
         <is>
-          <t>Baker</t>
+          <t>Umatilla</t>
         </is>
       </c>
       <c r="E270" s="23" t="inlineStr">
@@ -11622,7 +11622,7 @@
       </c>
       <c r="F270" s="23" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>11%</t>
         </is>
       </c>
       <c r="G270" s="23" t="n">
@@ -11632,12 +11632,12 @@
     <row r="271">
       <c r="A271" s="21" t="inlineStr">
         <is>
-          <t>97859</t>
+          <t>97814</t>
         </is>
       </c>
       <c r="B271" s="22" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-1406015-D</t>
+          <t>US-OR-BAK-BAB-1313</t>
         </is>
       </c>
       <c r="C271" s="22" t="inlineStr">
@@ -11647,7 +11647,7 @@
       </c>
       <c r="D271" s="22" t="inlineStr">
         <is>
-          <t>Umatilla</t>
+          <t>Baker</t>
         </is>
       </c>
       <c r="E271" s="21" t="inlineStr">
@@ -11667,22 +11667,22 @@
     <row r="272">
       <c r="A272" s="23" t="inlineStr">
         <is>
-          <t>97859</t>
+          <t>97028</t>
         </is>
       </c>
       <c r="B272" s="24" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-1406007-B</t>
+          <t>White River</t>
         </is>
       </c>
       <c r="C272" s="24" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="D272" s="24" t="inlineStr">
         <is>
-          <t>Umatilla</t>
+          <t>Clackamas, Hood River</t>
         </is>
       </c>
       <c r="E272" s="23" t="inlineStr">
@@ -11692,7 +11692,7 @@
       </c>
       <c r="F272" s="23" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G272" s="23" t="n">
@@ -11700,73 +11700,73 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="21" t="inlineStr">
-        <is>
-          <t>97814</t>
-        </is>
-      </c>
-      <c r="B273" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-BAK-BAB-1313</t>
-        </is>
-      </c>
-      <c r="C273" s="22" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D273" s="22" t="inlineStr">
-        <is>
-          <t>Baker</t>
-        </is>
-      </c>
-      <c r="E273" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F273" s="21" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G273" s="21" t="n">
-        <v>1</v>
+      <c r="A273" s="25" t="inlineStr">
+        <is>
+          <t>97028</t>
+        </is>
+      </c>
+      <c r="B273" s="26" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="C273" s="26" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="D273" s="26" t="inlineStr">
+        <is>
+          <t>Clackamas, Hood River</t>
+        </is>
+      </c>
+      <c r="E273" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F273" s="25" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="G273" s="25" t="n">
+        <v>565</v>
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="23" t="inlineStr">
+      <c r="A274" s="25" t="inlineStr">
         <is>
           <t>97028</t>
         </is>
       </c>
-      <c r="B274" s="24" t="inlineStr">
-        <is>
-          <t>White River</t>
-        </is>
-      </c>
-      <c r="C274" s="24" t="inlineStr">
+      <c r="B274" s="26" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="C274" s="26" t="inlineStr">
         <is>
           <t>Grasshopper</t>
         </is>
       </c>
-      <c r="D274" s="24" t="inlineStr">
+      <c r="D274" s="26" t="inlineStr">
         <is>
           <t>Clackamas, Hood River</t>
         </is>
       </c>
-      <c r="E274" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F274" s="23" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G274" s="23" t="n">
-        <v>1</v>
+      <c r="E274" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F274" s="25" t="inlineStr">
+        <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="G274" s="25" t="n">
+        <v>232</v>
       </c>
     </row>
     <row r="275">
@@ -11777,7 +11777,7 @@
       </c>
       <c r="B275" s="26" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>61</t>
         </is>
       </c>
       <c r="C275" s="26" t="inlineStr">
@@ -11797,361 +11797,361 @@
       </c>
       <c r="F275" s="25" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="G275" s="25" t="n">
-        <v>565</v>
+        <v>38</v>
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="25" t="inlineStr">
-        <is>
-          <t>97028</t>
-        </is>
-      </c>
-      <c r="B276" s="26" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="C276" s="26" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
-        </is>
-      </c>
-      <c r="D276" s="26" t="inlineStr">
-        <is>
-          <t>Clackamas, Hood River</t>
-        </is>
-      </c>
-      <c r="E276" s="25" t="inlineStr">
+      <c r="A276" s="23" t="inlineStr">
+        <is>
+          <t>97750</t>
+        </is>
+      </c>
+      <c r="B276" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-WHE-WHH-070</t>
+        </is>
+      </c>
+      <c r="C276" s="24" t="inlineStr">
+        <is>
+          <t>Rowe Creek Complex</t>
+        </is>
+      </c>
+      <c r="D276" s="24" t="inlineStr">
+        <is>
+          <t>Grant, Wheeler</t>
+        </is>
+      </c>
+      <c r="E276" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F276" s="23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G276" s="23" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="23" t="inlineStr">
+        <is>
+          <t>97750</t>
+        </is>
+      </c>
+      <c r="B277" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-WHE-WHH-068</t>
+        </is>
+      </c>
+      <c r="C277" s="24" t="inlineStr">
+        <is>
+          <t>Rowe Creek Complex</t>
+        </is>
+      </c>
+      <c r="D277" s="24" t="inlineStr">
+        <is>
+          <t>Grant, Wheeler</t>
+        </is>
+      </c>
+      <c r="E277" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F277" s="23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G277" s="23" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="23" t="inlineStr">
+        <is>
+          <t>97750</t>
+        </is>
+      </c>
+      <c r="B278" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-WHE-WHH-072-A</t>
+        </is>
+      </c>
+      <c r="C278" s="24" t="inlineStr">
+        <is>
+          <t>Rowe Creek Complex</t>
+        </is>
+      </c>
+      <c r="D278" s="24" t="inlineStr">
+        <is>
+          <t>Grant, Wheeler</t>
+        </is>
+      </c>
+      <c r="E278" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F278" s="23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G278" s="23" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="23" t="inlineStr">
+        <is>
+          <t>97750</t>
+        </is>
+      </c>
+      <c r="B279" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-WHE-WHH-072-C</t>
+        </is>
+      </c>
+      <c r="C279" s="24" t="inlineStr">
+        <is>
+          <t>Rowe Creek Complex</t>
+        </is>
+      </c>
+      <c r="D279" s="24" t="inlineStr">
+        <is>
+          <t>Grant, Wheeler</t>
+        </is>
+      </c>
+      <c r="E279" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F279" s="23" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="G279" s="23" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="23" t="inlineStr">
+        <is>
+          <t>97750</t>
+        </is>
+      </c>
+      <c r="B280" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-WHE-WHH-090-A</t>
+        </is>
+      </c>
+      <c r="C280" s="24" t="inlineStr">
+        <is>
+          <t>Rowe Creek Complex</t>
+        </is>
+      </c>
+      <c r="D280" s="24" t="inlineStr">
+        <is>
+          <t>Grant, Wheeler</t>
+        </is>
+      </c>
+      <c r="E280" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F280" s="23" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="G280" s="23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="25" t="inlineStr">
+        <is>
+          <t>97750</t>
+        </is>
+      </c>
+      <c r="B281" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-WHE-MIT-076</t>
+        </is>
+      </c>
+      <c r="C281" s="26" t="inlineStr">
+        <is>
+          <t>Rowe Creek Complex</t>
+        </is>
+      </c>
+      <c r="D281" s="26" t="inlineStr">
+        <is>
+          <t>Grant, Wheeler</t>
+        </is>
+      </c>
+      <c r="E281" s="25" t="inlineStr">
         <is>
           <t>Level 1 — GET READY</t>
         </is>
       </c>
-      <c r="F276" s="25" t="inlineStr">
-        <is>
-          <t>75%</t>
-        </is>
-      </c>
-      <c r="G276" s="25" t="n">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" s="25" t="inlineStr">
-        <is>
-          <t>97028</t>
-        </is>
-      </c>
-      <c r="B277" s="26" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="C277" s="26" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
-        </is>
-      </c>
-      <c r="D277" s="26" t="inlineStr">
-        <is>
-          <t>Clackamas, Hood River</t>
-        </is>
-      </c>
-      <c r="E277" s="25" t="inlineStr">
+      <c r="F281" s="25" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G281" s="25" t="n">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="25" t="inlineStr">
+        <is>
+          <t>97750</t>
+        </is>
+      </c>
+      <c r="B282" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-WHE-WHH-062</t>
+        </is>
+      </c>
+      <c r="C282" s="26" t="inlineStr">
+        <is>
+          <t>Rowe Creek Complex</t>
+        </is>
+      </c>
+      <c r="D282" s="26" t="inlineStr">
+        <is>
+          <t>Grant, Wheeler</t>
+        </is>
+      </c>
+      <c r="E282" s="25" t="inlineStr">
         <is>
           <t>Level 1 — GET READY</t>
         </is>
       </c>
-      <c r="F277" s="25" t="inlineStr">
-        <is>
-          <t>36%</t>
-        </is>
-      </c>
-      <c r="G277" s="25" t="n">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" s="25" t="inlineStr">
-        <is>
-          <t>97028</t>
-        </is>
-      </c>
-      <c r="B278" s="26" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="C278" s="26" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
-        </is>
-      </c>
-      <c r="D278" s="26" t="inlineStr">
-        <is>
-          <t>Clackamas, Hood River</t>
-        </is>
-      </c>
-      <c r="E278" s="25" t="inlineStr">
+      <c r="F282" s="25" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G282" s="25" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="25" t="inlineStr">
+        <is>
+          <t>97750</t>
+        </is>
+      </c>
+      <c r="B283" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-WHE-WHH-060-A</t>
+        </is>
+      </c>
+      <c r="C283" s="26" t="inlineStr">
+        <is>
+          <t>Rowe Creek Complex</t>
+        </is>
+      </c>
+      <c r="D283" s="26" t="inlineStr">
+        <is>
+          <t>Grant, Wheeler</t>
+        </is>
+      </c>
+      <c r="E283" s="25" t="inlineStr">
         <is>
           <t>Level 1 — GET READY</t>
         </is>
       </c>
-      <c r="F278" s="25" t="inlineStr">
-        <is>
-          <t>36%</t>
-        </is>
-      </c>
-      <c r="G278" s="25" t="n">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" s="25" t="inlineStr">
-        <is>
-          <t>97028</t>
-        </is>
-      </c>
-      <c r="B279" s="26" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="C279" s="26" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
-        </is>
-      </c>
-      <c r="D279" s="26" t="inlineStr">
-        <is>
-          <t>Clackamas, Hood River</t>
-        </is>
-      </c>
-      <c r="E279" s="25" t="inlineStr">
+      <c r="F283" s="25" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G283" s="25" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="25" t="inlineStr">
+        <is>
+          <t>97750</t>
+        </is>
+      </c>
+      <c r="B284" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-WHE-WHH-060-B</t>
+        </is>
+      </c>
+      <c r="C284" s="26" t="inlineStr">
+        <is>
+          <t>Rowe Creek Complex</t>
+        </is>
+      </c>
+      <c r="D284" s="26" t="inlineStr">
+        <is>
+          <t>Grant, Wheeler</t>
+        </is>
+      </c>
+      <c r="E284" s="25" t="inlineStr">
         <is>
           <t>Level 1 — GET READY</t>
         </is>
       </c>
-      <c r="F279" s="25" t="inlineStr">
-        <is>
-          <t>89%</t>
-        </is>
-      </c>
-      <c r="G279" s="25" t="n">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" s="25" t="inlineStr">
-        <is>
-          <t>97028</t>
-        </is>
-      </c>
-      <c r="B280" s="26" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="C280" s="26" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
-        </is>
-      </c>
-      <c r="D280" s="26" t="inlineStr">
-        <is>
-          <t>Clackamas, Hood River</t>
-        </is>
-      </c>
-      <c r="E280" s="25" t="inlineStr">
+      <c r="F284" s="25" t="inlineStr">
+        <is>
+          <t>86%</t>
+        </is>
+      </c>
+      <c r="G284" s="25" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="25" t="inlineStr">
+        <is>
+          <t>97750</t>
+        </is>
+      </c>
+      <c r="B285" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-WHE-WHH-054</t>
+        </is>
+      </c>
+      <c r="C285" s="26" t="inlineStr">
+        <is>
+          <t>Rowe Creek Complex</t>
+        </is>
+      </c>
+      <c r="D285" s="26" t="inlineStr">
+        <is>
+          <t>Grant, Wheeler</t>
+        </is>
+      </c>
+      <c r="E285" s="25" t="inlineStr">
         <is>
           <t>Level 1 — GET READY</t>
         </is>
       </c>
-      <c r="F280" s="25" t="inlineStr">
-        <is>
-          <t>89%</t>
-        </is>
-      </c>
-      <c r="G280" s="25" t="n">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" s="23" t="inlineStr">
-        <is>
-          <t>97750</t>
-        </is>
-      </c>
-      <c r="B281" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-WHE-WHH-070</t>
-        </is>
-      </c>
-      <c r="C281" s="24" t="inlineStr">
-        <is>
-          <t>Rowe Creek Complex</t>
-        </is>
-      </c>
-      <c r="D281" s="24" t="inlineStr">
-        <is>
-          <t>Grant, Wheeler</t>
-        </is>
-      </c>
-      <c r="E281" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F281" s="23" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G281" s="23" t="n">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" s="23" t="inlineStr">
-        <is>
-          <t>97750</t>
-        </is>
-      </c>
-      <c r="B282" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-WHE-WHH-068</t>
-        </is>
-      </c>
-      <c r="C282" s="24" t="inlineStr">
-        <is>
-          <t>Rowe Creek Complex</t>
-        </is>
-      </c>
-      <c r="D282" s="24" t="inlineStr">
-        <is>
-          <t>Grant, Wheeler</t>
-        </is>
-      </c>
-      <c r="E282" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F282" s="23" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G282" s="23" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" s="23" t="inlineStr">
-        <is>
-          <t>97750</t>
-        </is>
-      </c>
-      <c r="B283" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-WHE-WHH-072-A</t>
-        </is>
-      </c>
-      <c r="C283" s="24" t="inlineStr">
-        <is>
-          <t>Rowe Creek Complex</t>
-        </is>
-      </c>
-      <c r="D283" s="24" t="inlineStr">
-        <is>
-          <t>Grant, Wheeler</t>
-        </is>
-      </c>
-      <c r="E283" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F283" s="23" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G283" s="23" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" s="23" t="inlineStr">
-        <is>
-          <t>97750</t>
-        </is>
-      </c>
-      <c r="B284" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-WHE-WHH-072-C</t>
-        </is>
-      </c>
-      <c r="C284" s="24" t="inlineStr">
-        <is>
-          <t>Rowe Creek Complex</t>
-        </is>
-      </c>
-      <c r="D284" s="24" t="inlineStr">
-        <is>
-          <t>Grant, Wheeler</t>
-        </is>
-      </c>
-      <c r="E284" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F284" s="23" t="inlineStr">
-        <is>
-          <t>85%</t>
-        </is>
-      </c>
-      <c r="G284" s="23" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" s="23" t="inlineStr">
-        <is>
-          <t>97750</t>
-        </is>
-      </c>
-      <c r="B285" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-WHE-WHH-090-A</t>
-        </is>
-      </c>
-      <c r="C285" s="24" t="inlineStr">
-        <is>
-          <t>Rowe Creek Complex</t>
-        </is>
-      </c>
-      <c r="D285" s="24" t="inlineStr">
-        <is>
-          <t>Grant, Wheeler</t>
-        </is>
-      </c>
-      <c r="E285" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F285" s="23" t="inlineStr">
-        <is>
-          <t>18%</t>
-        </is>
-      </c>
-      <c r="G285" s="23" t="n">
-        <v>1</v>
+      <c r="F285" s="25" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="G285" s="25" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="286">
@@ -12162,7 +12162,7 @@
       </c>
       <c r="B286" s="26" t="inlineStr">
         <is>
-          <t>US-OR-WHE-MIT-076</t>
+          <t>US-OR-WHE-MIT-074</t>
         </is>
       </c>
       <c r="C286" s="26" t="inlineStr">
@@ -12186,7 +12186,7 @@
         </is>
       </c>
       <c r="G286" s="25" t="n">
-        <v>117</v>
+        <v>5</v>
       </c>
     </row>
     <row r="287">
@@ -12197,7 +12197,7 @@
       </c>
       <c r="B287" s="26" t="inlineStr">
         <is>
-          <t>US-OR-WHE-WHH-062</t>
+          <t>US-OR-WHE-MIT-078</t>
         </is>
       </c>
       <c r="C287" s="26" t="inlineStr">
@@ -12221,7 +12221,7 @@
         </is>
       </c>
       <c r="G287" s="25" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
     </row>
     <row r="288">
@@ -12232,12 +12232,12 @@
       </c>
       <c r="B288" s="26" t="inlineStr">
         <is>
-          <t>US-OR-WHE-WHH-060-A</t>
+          <t>US-OR-GRA-GRN-115</t>
         </is>
       </c>
       <c r="C288" s="26" t="inlineStr">
         <is>
-          <t>Rowe Creek Complex</t>
+          <t>Shingle</t>
         </is>
       </c>
       <c r="D288" s="26" t="inlineStr">
@@ -12252,102 +12252,102 @@
       </c>
       <c r="F288" s="25" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G288" s="25" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="289">
-      <c r="A289" s="25" t="inlineStr">
-        <is>
-          <t>97750</t>
-        </is>
-      </c>
-      <c r="B289" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-WHE-WHH-060-B</t>
-        </is>
-      </c>
-      <c r="C289" s="26" t="inlineStr">
-        <is>
-          <t>Rowe Creek Complex</t>
-        </is>
-      </c>
-      <c r="D289" s="26" t="inlineStr">
-        <is>
-          <t>Grant, Wheeler</t>
-        </is>
-      </c>
-      <c r="E289" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F289" s="25" t="inlineStr">
-        <is>
-          <t>86%</t>
-        </is>
-      </c>
-      <c r="G289" s="25" t="n">
-        <v>8</v>
+      <c r="A289" s="23" t="inlineStr">
+        <is>
+          <t>97876</t>
+        </is>
+      </c>
+      <c r="B289" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-UNI-UCO-1435</t>
+        </is>
+      </c>
+      <c r="C289" s="24" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D289" s="24" t="inlineStr">
+        <is>
+          <t>Union</t>
+        </is>
+      </c>
+      <c r="E289" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F289" s="23" t="inlineStr">
+        <is>
+          <t>74%</t>
+        </is>
+      </c>
+      <c r="G289" s="23" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="25" t="inlineStr">
-        <is>
-          <t>97750</t>
-        </is>
-      </c>
-      <c r="B290" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-WHE-WHH-054</t>
-        </is>
-      </c>
-      <c r="C290" s="26" t="inlineStr">
-        <is>
-          <t>Rowe Creek Complex</t>
-        </is>
-      </c>
-      <c r="D290" s="26" t="inlineStr">
-        <is>
-          <t>Grant, Wheeler</t>
-        </is>
-      </c>
-      <c r="E290" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F290" s="25" t="inlineStr">
-        <is>
-          <t>56%</t>
-        </is>
-      </c>
-      <c r="G290" s="25" t="n">
-        <v>5</v>
+      <c r="A290" s="23" t="inlineStr">
+        <is>
+          <t>97876</t>
+        </is>
+      </c>
+      <c r="B290" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-UNI-UCO-1450</t>
+        </is>
+      </c>
+      <c r="C290" s="24" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D290" s="24" t="inlineStr">
+        <is>
+          <t>Union</t>
+        </is>
+      </c>
+      <c r="E290" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F290" s="23" t="inlineStr">
+        <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="G290" s="23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="25" t="inlineStr">
         <is>
-          <t>97750</t>
+          <t>97876</t>
         </is>
       </c>
       <c r="B291" s="26" t="inlineStr">
         <is>
-          <t>US-OR-WHE-MIT-074</t>
+          <t>US-OR-UNI-UCO-1421</t>
         </is>
       </c>
       <c r="C291" s="26" t="inlineStr">
         <is>
-          <t>Rowe Creek Complex</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D291" s="26" t="inlineStr">
         <is>
-          <t>Grant, Wheeler</t>
+          <t>Union</t>
         </is>
       </c>
       <c r="E291" s="25" t="inlineStr">
@@ -12361,28 +12361,28 @@
         </is>
       </c>
       <c r="G291" s="25" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="25" t="inlineStr">
         <is>
-          <t>97750</t>
+          <t>97876</t>
         </is>
       </c>
       <c r="B292" s="26" t="inlineStr">
         <is>
-          <t>US-OR-WHE-MIT-078</t>
+          <t>US-OR-UNI-UCO-1436</t>
         </is>
       </c>
       <c r="C292" s="26" t="inlineStr">
         <is>
-          <t>Rowe Creek Complex</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D292" s="26" t="inlineStr">
         <is>
-          <t>Grant, Wheeler</t>
+          <t>Union</t>
         </is>
       </c>
       <c r="E292" s="25" t="inlineStr">
@@ -12396,28 +12396,28 @@
         </is>
       </c>
       <c r="G292" s="25" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="25" t="inlineStr">
         <is>
-          <t>97750</t>
+          <t>97876</t>
         </is>
       </c>
       <c r="B293" s="26" t="inlineStr">
         <is>
-          <t>US-OR-GRA-GRN-115</t>
+          <t>US-OR-UNI-UCO-1437</t>
         </is>
       </c>
       <c r="C293" s="26" t="inlineStr">
         <is>
-          <t>Shingle</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D293" s="26" t="inlineStr">
         <is>
-          <t>Grant, Wheeler</t>
+          <t>Union</t>
         </is>
       </c>
       <c r="E293" s="25" t="inlineStr">
@@ -12427,67 +12427,67 @@
       </c>
       <c r="F293" s="25" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G293" s="25" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="23" t="inlineStr">
+      <c r="A294" s="25" t="inlineStr">
         <is>
           <t>97876</t>
         </is>
       </c>
-      <c r="B294" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-UNI-UCO-1435</t>
-        </is>
-      </c>
-      <c r="C294" s="24" t="inlineStr">
+      <c r="B294" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-UNI-UCO-1438</t>
+        </is>
+      </c>
+      <c r="C294" s="26" t="inlineStr">
         <is>
           <t>No named fire</t>
         </is>
       </c>
-      <c r="D294" s="24" t="inlineStr">
+      <c r="D294" s="26" t="inlineStr">
         <is>
           <t>Union</t>
         </is>
       </c>
-      <c r="E294" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F294" s="23" t="inlineStr">
-        <is>
-          <t>74%</t>
-        </is>
-      </c>
-      <c r="G294" s="23" t="n">
-        <v>6</v>
+      <c r="E294" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F294" s="25" t="inlineStr">
+        <is>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="G294" s="25" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="23" t="inlineStr">
         <is>
-          <t>97876</t>
+          <t>97603</t>
         </is>
       </c>
       <c r="B295" s="24" t="inlineStr">
         <is>
-          <t>US-OR-UNI-UCO-1450</t>
+          <t>US-OR-KLA-KLA-1941</t>
         </is>
       </c>
       <c r="C295" s="24" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Wrights Spring</t>
         </is>
       </c>
       <c r="D295" s="24" t="inlineStr">
         <is>
-          <t>Union</t>
+          <t>Klamath</t>
         </is>
       </c>
       <c r="E295" s="23" t="inlineStr">
@@ -12497,32 +12497,32 @@
       </c>
       <c r="F295" s="23" t="inlineStr">
         <is>
-          <t>36%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="G295" s="23" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="25" t="inlineStr">
         <is>
-          <t>97876</t>
+          <t>97603</t>
         </is>
       </c>
       <c r="B296" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UNI-UCO-1421</t>
+          <t>US-OR-KLA-KLA-2261</t>
         </is>
       </c>
       <c r="C296" s="26" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Wrights Spring</t>
         </is>
       </c>
       <c r="D296" s="26" t="inlineStr">
         <is>
-          <t>Union</t>
+          <t>Klamath</t>
         </is>
       </c>
       <c r="E296" s="25" t="inlineStr">
@@ -12532,32 +12532,32 @@
       </c>
       <c r="F296" s="25" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>69%</t>
         </is>
       </c>
       <c r="G296" s="25" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="25" t="inlineStr">
         <is>
-          <t>97876</t>
+          <t>97603</t>
         </is>
       </c>
       <c r="B297" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UNI-UCO-1436</t>
+          <t>US-OR-KLA-KLA-1936</t>
         </is>
       </c>
       <c r="C297" s="26" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Wrights Spring</t>
         </is>
       </c>
       <c r="D297" s="26" t="inlineStr">
         <is>
-          <t>Union</t>
+          <t>Klamath</t>
         </is>
       </c>
       <c r="E297" s="25" t="inlineStr">
@@ -12571,28 +12571,28 @@
         </is>
       </c>
       <c r="G297" s="25" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="25" t="inlineStr">
         <is>
-          <t>97876</t>
+          <t>97603</t>
         </is>
       </c>
       <c r="B298" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UNI-UCO-1437</t>
+          <t>US-OR-KLA-KLA-2256</t>
         </is>
       </c>
       <c r="C298" s="26" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Wrights Spring</t>
         </is>
       </c>
       <c r="D298" s="26" t="inlineStr">
         <is>
-          <t>Union</t>
+          <t>Klamath</t>
         </is>
       </c>
       <c r="E298" s="25" t="inlineStr">
@@ -12602,172 +12602,172 @@
       </c>
       <c r="F298" s="25" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>72%</t>
         </is>
       </c>
       <c r="G298" s="25" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="25" t="inlineStr">
         <is>
-          <t>97876</t>
+          <t>97603</t>
         </is>
       </c>
       <c r="B299" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UNI-UCO-1438</t>
+          <t>US-OR-KLA-KLA-1931</t>
         </is>
       </c>
       <c r="C299" s="26" t="inlineStr">
         <is>
+          <t>Wrights Spring</t>
+        </is>
+      </c>
+      <c r="D299" s="26" t="inlineStr">
+        <is>
+          <t>Klamath</t>
+        </is>
+      </c>
+      <c r="E299" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F299" s="25" t="inlineStr">
+        <is>
+          <t>64%</t>
+        </is>
+      </c>
+      <c r="G299" s="25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="25" t="inlineStr">
+        <is>
+          <t>97603</t>
+        </is>
+      </c>
+      <c r="B300" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-1701</t>
+        </is>
+      </c>
+      <c r="C300" s="26" t="inlineStr">
+        <is>
+          <t>Wrights Spring</t>
+        </is>
+      </c>
+      <c r="D300" s="26" t="inlineStr">
+        <is>
+          <t>Klamath</t>
+        </is>
+      </c>
+      <c r="E300" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F300" s="25" t="inlineStr">
+        <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="G300" s="25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="23" t="inlineStr">
+        <is>
+          <t>97848</t>
+        </is>
+      </c>
+      <c r="B301" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-GRA-GRN-023</t>
+        </is>
+      </c>
+      <c r="C301" s="24" t="inlineStr">
+        <is>
           <t>No named fire</t>
         </is>
       </c>
-      <c r="D299" s="26" t="inlineStr">
-        <is>
-          <t>Union</t>
-        </is>
-      </c>
-      <c r="E299" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F299" s="25" t="inlineStr">
-        <is>
-          <t>99%</t>
-        </is>
-      </c>
-      <c r="G299" s="25" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" s="23" t="inlineStr">
-        <is>
-          <t>97603</t>
-        </is>
-      </c>
-      <c r="B300" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1941</t>
-        </is>
-      </c>
-      <c r="C300" s="24" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D300" s="24" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E300" s="23" t="inlineStr">
+      <c r="D301" s="24" t="inlineStr">
+        <is>
+          <t>Grant, Wheeler</t>
+        </is>
+      </c>
+      <c r="E301" s="23" t="inlineStr">
         <is>
           <t>Level 2 — GET SET</t>
         </is>
       </c>
-      <c r="F300" s="23" t="inlineStr">
-        <is>
-          <t>77%</t>
-        </is>
-      </c>
-      <c r="G300" s="23" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" s="25" t="inlineStr">
-        <is>
-          <t>97603</t>
-        </is>
-      </c>
-      <c r="B301" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-2261</t>
-        </is>
-      </c>
-      <c r="C301" s="26" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D301" s="26" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E301" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F301" s="25" t="inlineStr">
-        <is>
-          <t>69%</t>
-        </is>
-      </c>
-      <c r="G301" s="25" t="n">
-        <v>39</v>
+      <c r="F301" s="23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G301" s="23" t="n">
+        <v>47</v>
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="25" t="inlineStr">
-        <is>
-          <t>97603</t>
-        </is>
-      </c>
-      <c r="B302" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1936</t>
-        </is>
-      </c>
-      <c r="C302" s="26" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D302" s="26" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E302" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F302" s="25" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G302" s="25" t="n">
+      <c r="A302" s="23" t="inlineStr">
+        <is>
+          <t>97848</t>
+        </is>
+      </c>
+      <c r="B302" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-WHE-WHH-052-C</t>
+        </is>
+      </c>
+      <c r="C302" s="24" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D302" s="24" t="inlineStr">
+        <is>
+          <t>Grant, Wheeler</t>
+        </is>
+      </c>
+      <c r="E302" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F302" s="23" t="inlineStr">
+        <is>
+          <t>17%</t>
+        </is>
+      </c>
+      <c r="G302" s="23" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="25" t="inlineStr">
         <is>
-          <t>97603</t>
+          <t>97848</t>
         </is>
       </c>
       <c r="B303" s="26" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-2256</t>
+          <t>US-OR-GRA-DAY-117</t>
         </is>
       </c>
       <c r="C303" s="26" t="inlineStr">
         <is>
-          <t>Wrights Spring</t>
+          <t>Shingle</t>
         </is>
       </c>
       <c r="D303" s="26" t="inlineStr">
         <is>
-          <t>Klamath</t>
+          <t>Grant, Wheeler</t>
         </is>
       </c>
       <c r="E303" s="25" t="inlineStr">
@@ -12777,7 +12777,7 @@
       </c>
       <c r="F303" s="25" t="inlineStr">
         <is>
-          <t>72%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G303" s="25" t="n">
@@ -12787,22 +12787,22 @@
     <row r="304">
       <c r="A304" s="25" t="inlineStr">
         <is>
-          <t>97603</t>
+          <t>97848</t>
         </is>
       </c>
       <c r="B304" s="26" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1931</t>
+          <t>US-OR-GRA-GRN-115</t>
         </is>
       </c>
       <c r="C304" s="26" t="inlineStr">
         <is>
-          <t>Wrights Spring</t>
+          <t>Shingle</t>
         </is>
       </c>
       <c r="D304" s="26" t="inlineStr">
         <is>
-          <t>Klamath</t>
+          <t>Grant, Wheeler</t>
         </is>
       </c>
       <c r="E304" s="25" t="inlineStr">
@@ -12812,7 +12812,7 @@
       </c>
       <c r="F304" s="25" t="inlineStr">
         <is>
-          <t>64%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G304" s="25" t="n">
@@ -12820,59 +12820,59 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="25" t="inlineStr">
-        <is>
-          <t>97603</t>
-        </is>
-      </c>
-      <c r="B305" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1701</t>
-        </is>
-      </c>
-      <c r="C305" s="26" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D305" s="26" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E305" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F305" s="25" t="inlineStr">
-        <is>
-          <t>16%</t>
-        </is>
-      </c>
-      <c r="G305" s="25" t="n">
-        <v>1</v>
+      <c r="A305" s="23" t="inlineStr">
+        <is>
+          <t>97877</t>
+        </is>
+      </c>
+      <c r="B305" s="24" t="inlineStr">
+        <is>
+          <t>Salmon_3b</t>
+        </is>
+      </c>
+      <c r="C305" s="24" t="inlineStr">
+        <is>
+          <t>Salmon</t>
+        </is>
+      </c>
+      <c r="D305" s="24" t="inlineStr">
+        <is>
+          <t>Baker, Grant</t>
+        </is>
+      </c>
+      <c r="E305" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F305" s="23" t="inlineStr">
+        <is>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="G305" s="23" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="23" t="inlineStr">
         <is>
-          <t>97848</t>
+          <t>97877</t>
         </is>
       </c>
       <c r="B306" s="24" t="inlineStr">
         <is>
-          <t>US-OR-GRA-GRN-023</t>
+          <t>Olive_9</t>
         </is>
       </c>
       <c r="C306" s="24" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Salmon/Olive Butte Fires</t>
         </is>
       </c>
       <c r="D306" s="24" t="inlineStr">
         <is>
-          <t>Grant, Wheeler</t>
+          <t>Baker, Grant</t>
         </is>
       </c>
       <c r="E306" s="23" t="inlineStr">
@@ -12886,28 +12886,28 @@
         </is>
       </c>
       <c r="G306" s="23" t="n">
-        <v>47</v>
+        <v>7</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="23" t="inlineStr">
         <is>
-          <t>97848</t>
+          <t>97877</t>
         </is>
       </c>
       <c r="B307" s="24" t="inlineStr">
         <is>
-          <t>US-OR-WHE-WHH-052-C</t>
+          <t>Olive_3</t>
         </is>
       </c>
       <c r="C307" s="24" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Salmon/Olive Butte Fires</t>
         </is>
       </c>
       <c r="D307" s="24" t="inlineStr">
         <is>
-          <t>Grant, Wheeler</t>
+          <t>Baker, Grant</t>
         </is>
       </c>
       <c r="E307" s="23" t="inlineStr">
@@ -12917,81 +12917,81 @@
       </c>
       <c r="F307" s="23" t="inlineStr">
         <is>
-          <t>17%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G307" s="23" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="23" t="inlineStr">
+        <is>
+          <t>97877</t>
+        </is>
+      </c>
+      <c r="B308" s="24" t="inlineStr">
+        <is>
+          <t>Olive_7</t>
+        </is>
+      </c>
+      <c r="C308" s="24" t="inlineStr">
+        <is>
+          <t>Salmon/Olive Butte Fires</t>
+        </is>
+      </c>
+      <c r="D308" s="24" t="inlineStr">
+        <is>
+          <t>Baker, Grant</t>
+        </is>
+      </c>
+      <c r="E308" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F308" s="23" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="G308" s="23" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="308">
-      <c r="A308" s="25" t="inlineStr">
-        <is>
-          <t>97848</t>
-        </is>
-      </c>
-      <c r="B308" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-GRA-DAY-117</t>
-        </is>
-      </c>
-      <c r="C308" s="26" t="inlineStr">
-        <is>
-          <t>Shingle</t>
-        </is>
-      </c>
-      <c r="D308" s="26" t="inlineStr">
-        <is>
-          <t>Grant, Wheeler</t>
-        </is>
-      </c>
-      <c r="E308" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F308" s="25" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G308" s="25" t="n">
-        <v>1</v>
-      </c>
-    </row>
     <row r="309">
-      <c r="A309" s="25" t="inlineStr">
-        <is>
-          <t>97848</t>
-        </is>
-      </c>
-      <c r="B309" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-GRA-GRN-115</t>
-        </is>
-      </c>
-      <c r="C309" s="26" t="inlineStr">
-        <is>
-          <t>Shingle</t>
-        </is>
-      </c>
-      <c r="D309" s="26" t="inlineStr">
-        <is>
-          <t>Grant, Wheeler</t>
-        </is>
-      </c>
-      <c r="E309" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F309" s="25" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G309" s="25" t="n">
-        <v>1</v>
+      <c r="A309" s="23" t="inlineStr">
+        <is>
+          <t>97877</t>
+        </is>
+      </c>
+      <c r="B309" s="24" t="inlineStr">
+        <is>
+          <t>Olive_12</t>
+        </is>
+      </c>
+      <c r="C309" s="24" t="inlineStr">
+        <is>
+          <t>Salmon/Olive Butte Fires</t>
+        </is>
+      </c>
+      <c r="D309" s="24" t="inlineStr">
+        <is>
+          <t>Baker, Grant</t>
+        </is>
+      </c>
+      <c r="E309" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F309" s="23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G309" s="23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="310">
@@ -13002,12 +13002,12 @@
       </c>
       <c r="B310" s="24" t="inlineStr">
         <is>
-          <t>Salmon_3b</t>
+          <t>Salmon 12</t>
         </is>
       </c>
       <c r="C310" s="24" t="inlineStr">
         <is>
-          <t>Salmon</t>
+          <t>Salmon/Olive Butte Fires</t>
         </is>
       </c>
       <c r="D310" s="24" t="inlineStr">
@@ -13022,11 +13022,11 @@
       </c>
       <c r="F310" s="23" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="G310" s="23" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="311">
@@ -13037,7 +13037,7 @@
       </c>
       <c r="B311" s="24" t="inlineStr">
         <is>
-          <t>Olive_9</t>
+          <t>Olive_5</t>
         </is>
       </c>
       <c r="C311" s="24" t="inlineStr">
@@ -13061,7 +13061,7 @@
         </is>
       </c>
       <c r="G311" s="23" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="312">
@@ -13072,7 +13072,7 @@
       </c>
       <c r="B312" s="24" t="inlineStr">
         <is>
-          <t>Olive_3</t>
+          <t>Salmon_8</t>
         </is>
       </c>
       <c r="C312" s="24" t="inlineStr">
@@ -13092,32 +13092,32 @@
       </c>
       <c r="F312" s="23" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>72%</t>
         </is>
       </c>
       <c r="G312" s="23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="23" t="inlineStr">
         <is>
-          <t>97877</t>
+          <t>97856</t>
         </is>
       </c>
       <c r="B313" s="24" t="inlineStr">
         <is>
-          <t>Olive_7</t>
+          <t>US-OR-GRA-GRN-081</t>
         </is>
       </c>
       <c r="C313" s="24" t="inlineStr">
         <is>
-          <t>Salmon/Olive Butte Fires</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D313" s="24" t="inlineStr">
         <is>
-          <t>Baker, Grant</t>
+          <t>Grant</t>
         </is>
       </c>
       <c r="E313" s="23" t="inlineStr">
@@ -13127,32 +13127,32 @@
       </c>
       <c r="F313" s="23" t="inlineStr">
         <is>
-          <t>51%</t>
+          <t>44%</t>
         </is>
       </c>
       <c r="G313" s="23" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="23" t="inlineStr">
         <is>
-          <t>97877</t>
+          <t>97856</t>
         </is>
       </c>
       <c r="B314" s="24" t="inlineStr">
         <is>
-          <t>Olive_12</t>
+          <t>US-OR-GRA-GRN-099</t>
         </is>
       </c>
       <c r="C314" s="24" t="inlineStr">
         <is>
-          <t>Salmon/Olive Butte Fires</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D314" s="24" t="inlineStr">
         <is>
-          <t>Baker, Grant</t>
+          <t>Grant</t>
         </is>
       </c>
       <c r="E314" s="23" t="inlineStr">
@@ -13162,32 +13162,32 @@
       </c>
       <c r="F314" s="23" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>99%</t>
         </is>
       </c>
       <c r="G314" s="23" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="23" t="inlineStr">
         <is>
-          <t>97877</t>
+          <t>97856</t>
         </is>
       </c>
       <c r="B315" s="24" t="inlineStr">
         <is>
-          <t>Salmon 12</t>
+          <t>US-OR-GRA-GRN-079</t>
         </is>
       </c>
       <c r="C315" s="24" t="inlineStr">
         <is>
-          <t>Salmon/Olive Butte Fires</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D315" s="24" t="inlineStr">
         <is>
-          <t>Baker, Grant</t>
+          <t>Grant</t>
         </is>
       </c>
       <c r="E315" s="23" t="inlineStr">
@@ -13197,7 +13197,7 @@
       </c>
       <c r="F315" s="23" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="G315" s="23" t="n">
@@ -13205,59 +13205,59 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="23" t="inlineStr">
-        <is>
-          <t>97877</t>
-        </is>
-      </c>
-      <c r="B316" s="24" t="inlineStr">
-        <is>
-          <t>Olive_5</t>
-        </is>
-      </c>
-      <c r="C316" s="24" t="inlineStr">
-        <is>
-          <t>Salmon/Olive Butte Fires</t>
-        </is>
-      </c>
-      <c r="D316" s="24" t="inlineStr">
-        <is>
-          <t>Baker, Grant</t>
-        </is>
-      </c>
-      <c r="E316" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F316" s="23" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G316" s="23" t="n">
+      <c r="A316" s="25" t="inlineStr">
+        <is>
+          <t>97856</t>
+        </is>
+      </c>
+      <c r="B316" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-GRA-GRN-103</t>
+        </is>
+      </c>
+      <c r="C316" s="26" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D316" s="26" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="E316" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F316" s="25" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="G316" s="25" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="23" t="inlineStr">
         <is>
-          <t>97877</t>
+          <t>97864</t>
         </is>
       </c>
       <c r="B317" s="24" t="inlineStr">
         <is>
-          <t>Salmon_8</t>
+          <t>US-OR-GRA-GRN-081</t>
         </is>
       </c>
       <c r="C317" s="24" t="inlineStr">
         <is>
-          <t>Salmon/Olive Butte Fires</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D317" s="24" t="inlineStr">
         <is>
-          <t>Baker, Grant</t>
+          <t>Grant</t>
         </is>
       </c>
       <c r="E317" s="23" t="inlineStr">
@@ -13267,22 +13267,22 @@
       </c>
       <c r="F317" s="23" t="inlineStr">
         <is>
-          <t>72%</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="G317" s="23" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="23" t="inlineStr">
         <is>
-          <t>97856</t>
+          <t>97864</t>
         </is>
       </c>
       <c r="B318" s="24" t="inlineStr">
         <is>
-          <t>US-OR-GRA-GRN-081</t>
+          <t>US-OR-GRA-GRN-079</t>
         </is>
       </c>
       <c r="C318" s="24" t="inlineStr">
@@ -13302,22 +13302,22 @@
       </c>
       <c r="F318" s="23" t="inlineStr">
         <is>
-          <t>44%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="G318" s="23" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="23" t="inlineStr">
         <is>
-          <t>97856</t>
+          <t>97864</t>
         </is>
       </c>
       <c r="B319" s="24" t="inlineStr">
         <is>
-          <t>US-OR-GRA-GRN-099</t>
+          <t>US-OR-GRA-GRN-023</t>
         </is>
       </c>
       <c r="C319" s="24" t="inlineStr">
@@ -13337,137 +13337,137 @@
       </c>
       <c r="F319" s="23" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G319" s="23" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="23" t="inlineStr">
-        <is>
-          <t>97856</t>
-        </is>
-      </c>
-      <c r="B320" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-GRA-GRN-079</t>
-        </is>
-      </c>
-      <c r="C320" s="24" t="inlineStr">
+      <c r="A320" s="25" t="inlineStr">
+        <is>
+          <t>97864</t>
+        </is>
+      </c>
+      <c r="B320" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-GRA-GRN-077</t>
+        </is>
+      </c>
+      <c r="C320" s="26" t="inlineStr">
         <is>
           <t>No named fire</t>
         </is>
       </c>
-      <c r="D320" s="24" t="inlineStr">
+      <c r="D320" s="26" t="inlineStr">
         <is>
           <t>Grant</t>
         </is>
       </c>
-      <c r="E320" s="23" t="inlineStr">
+      <c r="E320" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F320" s="25" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="G320" s="25" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="23" t="inlineStr">
+        <is>
+          <t>97874</t>
+        </is>
+      </c>
+      <c r="B321" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-WHE-WHH-052-C</t>
+        </is>
+      </c>
+      <c r="C321" s="24" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D321" s="24" t="inlineStr">
+        <is>
+          <t>Wheeler</t>
+        </is>
+      </c>
+      <c r="E321" s="23" t="inlineStr">
         <is>
           <t>Level 2 — GET SET</t>
         </is>
       </c>
-      <c r="F320" s="23" t="inlineStr">
-        <is>
-          <t>20%</t>
-        </is>
-      </c>
-      <c r="G320" s="23" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="321">
-      <c r="A321" s="25" t="inlineStr">
-        <is>
-          <t>97856</t>
-        </is>
-      </c>
-      <c r="B321" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-GRA-GRN-103</t>
-        </is>
-      </c>
-      <c r="C321" s="26" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D321" s="26" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
-      <c r="E321" s="25" t="inlineStr">
+      <c r="F321" s="23" t="inlineStr">
+        <is>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="G321" s="23" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="25" t="inlineStr">
+        <is>
+          <t>97874</t>
+        </is>
+      </c>
+      <c r="B322" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-WHE-WHH-054</t>
+        </is>
+      </c>
+      <c r="C322" s="26" t="inlineStr">
+        <is>
+          <t>Rowe Creek Complex</t>
+        </is>
+      </c>
+      <c r="D322" s="26" t="inlineStr">
+        <is>
+          <t>Wheeler</t>
+        </is>
+      </c>
+      <c r="E322" s="25" t="inlineStr">
         <is>
           <t>Level 1 — GET READY</t>
         </is>
       </c>
-      <c r="F321" s="25" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G321" s="25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322" s="23" t="inlineStr">
-        <is>
-          <t>97864</t>
-        </is>
-      </c>
-      <c r="B322" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-GRA-GRN-081</t>
-        </is>
-      </c>
-      <c r="C322" s="24" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D322" s="24" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
-      <c r="E322" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F322" s="23" t="inlineStr">
-        <is>
-          <t>56%</t>
-        </is>
-      </c>
-      <c r="G322" s="23" t="n">
-        <v>17</v>
+      <c r="F322" s="25" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="G322" s="25" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="23" t="inlineStr">
         <is>
-          <t>97864</t>
+          <t>97817</t>
         </is>
       </c>
       <c r="B323" s="24" t="inlineStr">
         <is>
-          <t>US-OR-GRA-GRN-079</t>
+          <t>Salmon 12</t>
         </is>
       </c>
       <c r="C323" s="24" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Salmon/Olive Butte Fires</t>
         </is>
       </c>
       <c r="D323" s="24" t="inlineStr">
         <is>
-          <t>Grant</t>
+          <t>Baker, Grant</t>
         </is>
       </c>
       <c r="E323" s="23" t="inlineStr">
@@ -13477,32 +13477,32 @@
       </c>
       <c r="F323" s="23" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="G323" s="23" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="23" t="inlineStr">
         <is>
-          <t>97864</t>
+          <t>97817</t>
         </is>
       </c>
       <c r="B324" s="24" t="inlineStr">
         <is>
-          <t>US-OR-GRA-GRN-023</t>
+          <t>Olive_7</t>
         </is>
       </c>
       <c r="C324" s="24" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Salmon/Olive Butte Fires</t>
         </is>
       </c>
       <c r="D324" s="24" t="inlineStr">
         <is>
-          <t>Grant</t>
+          <t>Baker, Grant</t>
         </is>
       </c>
       <c r="E324" s="23" t="inlineStr">
@@ -13512,137 +13512,137 @@
       </c>
       <c r="F324" s="23" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>49%</t>
         </is>
       </c>
       <c r="G324" s="23" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="23" t="inlineStr">
+        <is>
+          <t>97817</t>
+        </is>
+      </c>
+      <c r="B325" s="24" t="inlineStr">
+        <is>
+          <t>Salmon_8</t>
+        </is>
+      </c>
+      <c r="C325" s="24" t="inlineStr">
+        <is>
+          <t>Salmon/Olive Butte Fires</t>
+        </is>
+      </c>
+      <c r="D325" s="24" t="inlineStr">
+        <is>
+          <t>Baker, Grant</t>
+        </is>
+      </c>
+      <c r="E325" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F325" s="23" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="G325" s="23" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325" s="25" t="inlineStr">
-        <is>
-          <t>97864</t>
-        </is>
-      </c>
-      <c r="B325" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-GRA-GRN-077</t>
-        </is>
-      </c>
-      <c r="C325" s="26" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D325" s="26" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
-      <c r="E325" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F325" s="25" t="inlineStr">
-        <is>
-          <t>65%</t>
-        </is>
-      </c>
-      <c r="G325" s="25" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="23" t="inlineStr">
         <is>
-          <t>97874</t>
+          <t>97817</t>
         </is>
       </c>
       <c r="B326" s="24" t="inlineStr">
         <is>
-          <t>US-OR-WHE-WHH-052-C</t>
+          <t>Salmon_3b</t>
         </is>
       </c>
       <c r="C326" s="24" t="inlineStr">
         <is>
+          <t>Salmon</t>
+        </is>
+      </c>
+      <c r="D326" s="24" t="inlineStr">
+        <is>
+          <t>Baker, Grant</t>
+        </is>
+      </c>
+      <c r="E326" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F326" s="23" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="G326" s="23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="23" t="inlineStr">
+        <is>
+          <t>97865</t>
+        </is>
+      </c>
+      <c r="B327" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-GRA-GRN-099</t>
+        </is>
+      </c>
+      <c r="C327" s="24" t="inlineStr">
+        <is>
           <t>No named fire</t>
         </is>
       </c>
-      <c r="D326" s="24" t="inlineStr">
-        <is>
-          <t>Wheeler</t>
-        </is>
-      </c>
-      <c r="E326" s="23" t="inlineStr">
+      <c r="D327" s="24" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="E327" s="23" t="inlineStr">
         <is>
           <t>Level 2 — GET SET</t>
         </is>
       </c>
-      <c r="F326" s="23" t="inlineStr">
-        <is>
-          <t>83%</t>
-        </is>
-      </c>
-      <c r="G326" s="23" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="327">
-      <c r="A327" s="25" t="inlineStr">
-        <is>
-          <t>97874</t>
-        </is>
-      </c>
-      <c r="B327" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-WHE-WHH-054</t>
-        </is>
-      </c>
-      <c r="C327" s="26" t="inlineStr">
-        <is>
-          <t>Rowe Creek Complex</t>
-        </is>
-      </c>
-      <c r="D327" s="26" t="inlineStr">
-        <is>
-          <t>Wheeler</t>
-        </is>
-      </c>
-      <c r="E327" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F327" s="25" t="inlineStr">
-        <is>
-          <t>44%</t>
-        </is>
-      </c>
-      <c r="G327" s="25" t="n">
-        <v>4</v>
+      <c r="F327" s="23" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="G327" s="23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="23" t="inlineStr">
         <is>
-          <t>97817</t>
+          <t>97865</t>
         </is>
       </c>
       <c r="B328" s="24" t="inlineStr">
         <is>
-          <t>Salmon 12</t>
+          <t>US-OR-GRA-GRN-079</t>
         </is>
       </c>
       <c r="C328" s="24" t="inlineStr">
         <is>
-          <t>Salmon/Olive Butte Fires</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D328" s="24" t="inlineStr">
         <is>
-          <t>Baker, Grant</t>
+          <t>Grant</t>
         </is>
       </c>
       <c r="E328" s="23" t="inlineStr">
@@ -13652,102 +13652,102 @@
       </c>
       <c r="F328" s="23" t="inlineStr">
         <is>
-          <t>87%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="G328" s="23" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="329">
-      <c r="A329" s="23" t="inlineStr">
-        <is>
-          <t>97817</t>
-        </is>
-      </c>
-      <c r="B329" s="24" t="inlineStr">
-        <is>
-          <t>Olive_7</t>
-        </is>
-      </c>
-      <c r="C329" s="24" t="inlineStr">
-        <is>
-          <t>Salmon/Olive Butte Fires</t>
-        </is>
-      </c>
-      <c r="D329" s="24" t="inlineStr">
-        <is>
-          <t>Baker, Grant</t>
-        </is>
-      </c>
-      <c r="E329" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F329" s="23" t="inlineStr">
-        <is>
-          <t>49%</t>
-        </is>
-      </c>
-      <c r="G329" s="23" t="n">
-        <v>2</v>
+      <c r="A329" s="25" t="inlineStr">
+        <is>
+          <t>97865</t>
+        </is>
+      </c>
+      <c r="B329" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-GRA-GRN-137</t>
+        </is>
+      </c>
+      <c r="C329" s="26" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D329" s="26" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="E329" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F329" s="25" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="G329" s="25" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="330">
-      <c r="A330" s="23" t="inlineStr">
-        <is>
-          <t>97817</t>
-        </is>
-      </c>
-      <c r="B330" s="24" t="inlineStr">
-        <is>
-          <t>Salmon_8</t>
-        </is>
-      </c>
-      <c r="C330" s="24" t="inlineStr">
-        <is>
-          <t>Salmon/Olive Butte Fires</t>
-        </is>
-      </c>
-      <c r="D330" s="24" t="inlineStr">
-        <is>
-          <t>Baker, Grant</t>
-        </is>
-      </c>
-      <c r="E330" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F330" s="23" t="inlineStr">
-        <is>
-          <t>28%</t>
-        </is>
-      </c>
-      <c r="G330" s="23" t="n">
+      <c r="A330" s="25" t="inlineStr">
+        <is>
+          <t>97865</t>
+        </is>
+      </c>
+      <c r="B330" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-GRA-GRN-103</t>
+        </is>
+      </c>
+      <c r="C330" s="26" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D330" s="26" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="E330" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F330" s="25" t="inlineStr">
+        <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="G330" s="25" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="23" t="inlineStr">
         <is>
-          <t>97817</t>
+          <t>99362</t>
         </is>
       </c>
       <c r="B331" s="24" t="inlineStr">
         <is>
-          <t>Salmon_3b</t>
+          <t>US-OR-UMA-UMC-1406043-C</t>
         </is>
       </c>
       <c r="C331" s="24" t="inlineStr">
         <is>
-          <t>Salmon</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D331" s="24" t="inlineStr">
         <is>
-          <t>Baker, Grant</t>
+          <t>Umatilla</t>
         </is>
       </c>
       <c r="E331" s="23" t="inlineStr">
@@ -13757,32 +13757,32 @@
       </c>
       <c r="F331" s="23" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G331" s="23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="23" t="inlineStr">
         <is>
-          <t>97865</t>
+          <t>97037</t>
         </is>
       </c>
       <c r="B332" s="24" t="inlineStr">
         <is>
-          <t>US-OR-GRA-GRN-099</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="C332" s="24" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="D332" s="24" t="inlineStr">
         <is>
-          <t>Grant</t>
+          <t>Wasco</t>
         </is>
       </c>
       <c r="E332" s="23" t="inlineStr">
@@ -13792,7 +13792,7 @@
       </c>
       <c r="F332" s="23" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G332" s="23" t="n">
@@ -13800,189 +13800,189 @@
       </c>
     </row>
     <row r="333">
-      <c r="A333" s="23" t="inlineStr">
-        <is>
-          <t>97865</t>
-        </is>
-      </c>
-      <c r="B333" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-GRA-GRN-079</t>
-        </is>
-      </c>
-      <c r="C333" s="24" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D333" s="24" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
-      <c r="E333" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F333" s="23" t="inlineStr">
-        <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="G333" s="23" t="n">
-        <v>1</v>
+      <c r="A333" s="25" t="inlineStr">
+        <is>
+          <t>97037</t>
+        </is>
+      </c>
+      <c r="B333" s="26" t="inlineStr">
+        <is>
+          <t>KM</t>
+        </is>
+      </c>
+      <c r="C333" s="26" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="D333" s="26" t="inlineStr">
+        <is>
+          <t>Wasco</t>
+        </is>
+      </c>
+      <c r="E333" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F333" s="25" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="G333" s="25" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="25" t="inlineStr">
         <is>
-          <t>97865</t>
+          <t>97037</t>
         </is>
       </c>
       <c r="B334" s="26" t="inlineStr">
         <is>
-          <t>US-OR-GRA-GRN-137</t>
+          <t>SBR</t>
         </is>
       </c>
       <c r="C334" s="26" t="inlineStr">
         <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="D334" s="26" t="inlineStr">
+        <is>
+          <t>Wasco</t>
+        </is>
+      </c>
+      <c r="E334" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F334" s="25" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="G334" s="25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="23" t="inlineStr">
+        <is>
+          <t>97840</t>
+        </is>
+      </c>
+      <c r="B335" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-BAK-RCH-570</t>
+        </is>
+      </c>
+      <c r="C335" s="24" t="inlineStr">
+        <is>
           <t>No named fire</t>
         </is>
       </c>
-      <c r="D334" s="26" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
-      <c r="E334" s="25" t="inlineStr">
+      <c r="D335" s="24" t="inlineStr">
+        <is>
+          <t>Baker</t>
+        </is>
+      </c>
+      <c r="E335" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F335" s="23" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="G335" s="23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="25" t="inlineStr">
+        <is>
+          <t>97049</t>
+        </is>
+      </c>
+      <c r="B336" s="26" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="C336" s="26" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="D336" s="26" t="inlineStr">
+        <is>
+          <t>Clackamas</t>
+        </is>
+      </c>
+      <c r="E336" s="25" t="inlineStr">
         <is>
           <t>Level 1 — GET READY</t>
         </is>
       </c>
-      <c r="F334" s="25" t="inlineStr">
-        <is>
-          <t>30%</t>
-        </is>
-      </c>
-      <c r="G334" s="25" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" s="25" t="inlineStr">
-        <is>
-          <t>97865</t>
-        </is>
-      </c>
-      <c r="B335" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-GRA-GRN-103</t>
-        </is>
-      </c>
-      <c r="C335" s="26" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D335" s="26" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
-      <c r="E335" s="25" t="inlineStr">
+      <c r="F336" s="25" t="inlineStr">
+        <is>
+          <t>63%</t>
+        </is>
+      </c>
+      <c r="G336" s="25" t="n">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="25" t="inlineStr">
+        <is>
+          <t>97049</t>
+        </is>
+      </c>
+      <c r="B337" s="26" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="C337" s="26" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="D337" s="26" t="inlineStr">
+        <is>
+          <t>Clackamas</t>
+        </is>
+      </c>
+      <c r="E337" s="25" t="inlineStr">
         <is>
           <t>Level 1 — GET READY</t>
         </is>
       </c>
-      <c r="F335" s="25" t="inlineStr">
-        <is>
-          <t>34%</t>
-        </is>
-      </c>
-      <c r="G335" s="25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" s="23" t="inlineStr">
-        <is>
-          <t>99362</t>
-        </is>
-      </c>
-      <c r="B336" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-1406043-C</t>
-        </is>
-      </c>
-      <c r="C336" s="24" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D336" s="24" t="inlineStr">
-        <is>
-          <t>Umatilla</t>
-        </is>
-      </c>
-      <c r="E336" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F336" s="23" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G336" s="23" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" s="23" t="inlineStr">
-        <is>
-          <t>97037</t>
-        </is>
-      </c>
-      <c r="B337" s="24" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="C337" s="24" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
-        </is>
-      </c>
-      <c r="D337" s="24" t="inlineStr">
-        <is>
-          <t>Wasco</t>
-        </is>
-      </c>
-      <c r="E337" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F337" s="23" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G337" s="23" t="n">
-        <v>1</v>
+      <c r="F337" s="25" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="G337" s="25" t="n">
+        <v>186</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="25" t="inlineStr">
         <is>
-          <t>97037</t>
+          <t>97049</t>
         </is>
       </c>
       <c r="B338" s="26" t="inlineStr">
         <is>
-          <t>KM</t>
+          <t>66</t>
         </is>
       </c>
       <c r="C338" s="26" t="inlineStr">
@@ -13992,7 +13992,7 @@
       </c>
       <c r="D338" s="26" t="inlineStr">
         <is>
-          <t>Wasco</t>
+          <t>Clackamas</t>
         </is>
       </c>
       <c r="E338" s="25" t="inlineStr">
@@ -14002,32 +14002,32 @@
       </c>
       <c r="F338" s="25" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G338" s="25" t="n">
-        <v>3</v>
+        <v>88</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="25" t="inlineStr">
         <is>
-          <t>97037</t>
+          <t>97478</t>
         </is>
       </c>
       <c r="B339" s="26" t="inlineStr">
         <is>
-          <t>SBR</t>
+          <t>US-OR-LAN-SPR-0940</t>
         </is>
       </c>
       <c r="C339" s="26" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D339" s="26" t="inlineStr">
         <is>
-          <t>Wasco</t>
+          <t>Lane</t>
         </is>
       </c>
       <c r="E339" s="25" t="inlineStr">
@@ -14037,67 +14037,67 @@
       </c>
       <c r="F339" s="25" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G339" s="25" t="n">
-        <v>1</v>
+        <v>316</v>
       </c>
     </row>
     <row r="340">
-      <c r="A340" s="23" t="inlineStr">
-        <is>
-          <t>97840</t>
-        </is>
-      </c>
-      <c r="B340" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-BAK-RCH-570</t>
-        </is>
-      </c>
-      <c r="C340" s="24" t="inlineStr">
+      <c r="A340" s="25" t="inlineStr">
+        <is>
+          <t>97478</t>
+        </is>
+      </c>
+      <c r="B340" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-LAN-SPR-0952-A</t>
+        </is>
+      </c>
+      <c r="C340" s="26" t="inlineStr">
         <is>
           <t>No named fire</t>
         </is>
       </c>
-      <c r="D340" s="24" t="inlineStr">
-        <is>
-          <t>Baker</t>
-        </is>
-      </c>
-      <c r="E340" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F340" s="23" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G340" s="23" t="n">
-        <v>1</v>
+      <c r="D340" s="26" t="inlineStr">
+        <is>
+          <t>Lane</t>
+        </is>
+      </c>
+      <c r="E340" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F340" s="25" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G340" s="25" t="n">
+        <v>72</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="25" t="inlineStr">
         <is>
-          <t>97049</t>
+          <t>97825</t>
         </is>
       </c>
       <c r="B341" s="26" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>US-OR-GRA-DAY-117</t>
         </is>
       </c>
       <c r="C341" s="26" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Shingle</t>
         </is>
       </c>
       <c r="D341" s="26" t="inlineStr">
         <is>
-          <t>Clackamas</t>
+          <t>Grant</t>
         </is>
       </c>
       <c r="E341" s="25" t="inlineStr">
@@ -14107,32 +14107,32 @@
       </c>
       <c r="F341" s="25" t="inlineStr">
         <is>
-          <t>63%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G341" s="25" t="n">
-        <v>403</v>
+        <v>99</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="25" t="inlineStr">
         <is>
-          <t>97049</t>
+          <t>97825</t>
         </is>
       </c>
       <c r="B342" s="26" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>US-OR-GRA-GRN-115</t>
         </is>
       </c>
       <c r="C342" s="26" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Shingle</t>
         </is>
       </c>
       <c r="D342" s="26" t="inlineStr">
         <is>
-          <t>Clackamas</t>
+          <t>Grant</t>
         </is>
       </c>
       <c r="E342" s="25" t="inlineStr">
@@ -14142,32 +14142,32 @@
       </c>
       <c r="F342" s="25" t="inlineStr">
         <is>
-          <t>63%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G342" s="25" t="n">
-        <v>403</v>
+        <v>24</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="25" t="inlineStr">
         <is>
-          <t>97049</t>
+          <t>97825</t>
         </is>
       </c>
       <c r="B343" s="26" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>US-OR-GRA-GRN-153</t>
         </is>
       </c>
       <c r="C343" s="26" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Shingle</t>
         </is>
       </c>
       <c r="D343" s="26" t="inlineStr">
         <is>
-          <t>Clackamas</t>
+          <t>Grant</t>
         </is>
       </c>
       <c r="E343" s="25" t="inlineStr">
@@ -14177,32 +14177,32 @@
       </c>
       <c r="F343" s="25" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G343" s="25" t="n">
-        <v>186</v>
+        <v>12</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="25" t="inlineStr">
         <is>
-          <t>97049</t>
+          <t>97497</t>
         </is>
       </c>
       <c r="B344" s="26" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>US-OR-JOS-JCU-302-B</t>
         </is>
       </c>
       <c r="C344" s="26" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D344" s="26" t="inlineStr">
         <is>
-          <t>Clackamas</t>
+          <t>Josephine</t>
         </is>
       </c>
       <c r="E344" s="25" t="inlineStr">
@@ -14212,32 +14212,32 @@
       </c>
       <c r="F344" s="25" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G344" s="25" t="n">
-        <v>186</v>
+        <v>104</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="25" t="inlineStr">
         <is>
-          <t>97049</t>
+          <t>97833</t>
         </is>
       </c>
       <c r="B345" s="26" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C345" s="26" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Anthony Fire</t>
         </is>
       </c>
       <c r="D345" s="26" t="inlineStr">
         <is>
-          <t>Clackamas</t>
+          <t>Baker</t>
         </is>
       </c>
       <c r="E345" s="25" t="inlineStr">
@@ -14247,32 +14247,32 @@
       </c>
       <c r="F345" s="25" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>99%</t>
         </is>
       </c>
       <c r="G345" s="25" t="n">
-        <v>88</v>
+        <v>23</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="25" t="inlineStr">
         <is>
-          <t>97049</t>
+          <t>97828</t>
         </is>
       </c>
       <c r="B346" s="26" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>BC1</t>
         </is>
       </c>
       <c r="C346" s="26" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Burnt Creek Fire</t>
         </is>
       </c>
       <c r="D346" s="26" t="inlineStr">
         <is>
-          <t>Clackamas</t>
+          <t>Wallowa</t>
         </is>
       </c>
       <c r="E346" s="25" t="inlineStr">
@@ -14282,22 +14282,22 @@
       </c>
       <c r="F346" s="25" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>92%</t>
         </is>
       </c>
       <c r="G346" s="25" t="n">
-        <v>88</v>
+        <v>17</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="25" t="inlineStr">
         <is>
-          <t>97478</t>
+          <t>97845</t>
         </is>
       </c>
       <c r="B347" s="26" t="inlineStr">
         <is>
-          <t>US-OR-LAN-SPR-0940</t>
+          <t>US-OR-GRA-GRN-137</t>
         </is>
       </c>
       <c r="C347" s="26" t="inlineStr">
@@ -14307,7 +14307,7 @@
       </c>
       <c r="D347" s="26" t="inlineStr">
         <is>
-          <t>Lane</t>
+          <t>Grant</t>
         </is>
       </c>
       <c r="E347" s="25" t="inlineStr">
@@ -14317,32 +14317,32 @@
       </c>
       <c r="F347" s="25" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="G347" s="25" t="n">
-        <v>316</v>
+        <v>7</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="25" t="inlineStr">
         <is>
-          <t>97478</t>
+          <t>97711</t>
         </is>
       </c>
       <c r="B348" s="26" t="inlineStr">
         <is>
-          <t>US-OR-LAN-SPR-0952-A</t>
+          <t>NE 15 East</t>
         </is>
       </c>
       <c r="C348" s="26" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Rowe Creek Complex</t>
         </is>
       </c>
       <c r="D348" s="26" t="inlineStr">
         <is>
-          <t>Lane</t>
+          <t>Jefferson</t>
         </is>
       </c>
       <c r="E348" s="25" t="inlineStr">
@@ -14356,28 +14356,28 @@
         </is>
       </c>
       <c r="G348" s="25" t="n">
-        <v>72</v>
+        <v>1</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="25" t="inlineStr">
         <is>
-          <t>97825</t>
+          <t>97067</t>
         </is>
       </c>
       <c r="B349" s="26" t="inlineStr">
         <is>
-          <t>US-OR-GRA-DAY-117</t>
+          <t>59</t>
         </is>
       </c>
       <c r="C349" s="26" t="inlineStr">
         <is>
-          <t>Shingle</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="D349" s="26" t="inlineStr">
         <is>
-          <t>Grant</t>
+          <t>Clackamas</t>
         </is>
       </c>
       <c r="E349" s="25" t="inlineStr">
@@ -14387,32 +14387,32 @@
       </c>
       <c r="F349" s="25" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G349" s="25" t="n">
-        <v>99</v>
+        <v>1</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="25" t="inlineStr">
         <is>
-          <t>97825</t>
+          <t>97442</t>
         </is>
       </c>
       <c r="B350" s="26" t="inlineStr">
         <is>
-          <t>US-OR-GRA-GRN-115</t>
+          <t>US-OR-JOS-JCU-302-B</t>
         </is>
       </c>
       <c r="C350" s="26" t="inlineStr">
         <is>
-          <t>Shingle</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D350" s="26" t="inlineStr">
         <is>
-          <t>Grant</t>
+          <t>Josephine</t>
         </is>
       </c>
       <c r="E350" s="25" t="inlineStr">
@@ -14422,32 +14422,32 @@
       </c>
       <c r="F350" s="25" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G350" s="25" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="25" t="inlineStr">
         <is>
-          <t>97825</t>
+          <t>97029</t>
         </is>
       </c>
       <c r="B351" s="26" t="inlineStr">
         <is>
-          <t>US-OR-GRA-GRN-153</t>
+          <t>LDWT</t>
         </is>
       </c>
       <c r="C351" s="26" t="inlineStr">
         <is>
-          <t>Shingle</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="D351" s="26" t="inlineStr">
         <is>
-          <t>Grant</t>
+          <t>Wasco</t>
         </is>
       </c>
       <c r="E351" s="25" t="inlineStr">
@@ -14457,32 +14457,32 @@
       </c>
       <c r="F351" s="25" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="G351" s="25" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="25" t="inlineStr">
         <is>
-          <t>97497</t>
+          <t>97029</t>
         </is>
       </c>
       <c r="B352" s="26" t="inlineStr">
         <is>
-          <t>US-OR-JOS-JCU-302-B</t>
+          <t>SBR</t>
         </is>
       </c>
       <c r="C352" s="26" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="D352" s="26" t="inlineStr">
         <is>
-          <t>Josephine</t>
+          <t>Wasco</t>
         </is>
       </c>
       <c r="E352" s="25" t="inlineStr">
@@ -14492,32 +14492,32 @@
       </c>
       <c r="F352" s="25" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G352" s="25" t="n">
-        <v>104</v>
+        <v>1</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="25" t="inlineStr">
         <is>
-          <t>97833</t>
+          <t>97040</t>
         </is>
       </c>
       <c r="B353" s="26" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>MCR</t>
         </is>
       </c>
       <c r="C353" s="26" t="inlineStr">
         <is>
-          <t>Anthony Fire</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="D353" s="26" t="inlineStr">
         <is>
-          <t>Baker</t>
+          <t>Wasco</t>
         </is>
       </c>
       <c r="E353" s="25" t="inlineStr">
@@ -14527,32 +14527,32 @@
       </c>
       <c r="F353" s="25" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G353" s="25" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="25" t="inlineStr">
         <is>
-          <t>97828</t>
+          <t>97601</t>
         </is>
       </c>
       <c r="B354" s="26" t="inlineStr">
         <is>
-          <t>BC1</t>
+          <t>US-OR-KLA-KLA-1931</t>
         </is>
       </c>
       <c r="C354" s="26" t="inlineStr">
         <is>
-          <t>Burnt Creek Fire</t>
+          <t>Wrights Spring</t>
         </is>
       </c>
       <c r="D354" s="26" t="inlineStr">
         <is>
-          <t>Wallowa</t>
+          <t>Klamath</t>
         </is>
       </c>
       <c r="E354" s="25" t="inlineStr">
@@ -14562,330 +14562,15 @@
       </c>
       <c r="F354" s="25" t="inlineStr">
         <is>
-          <t>92%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G354" s="25" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="355">
-      <c r="A355" s="25" t="inlineStr">
-        <is>
-          <t>97845</t>
-        </is>
-      </c>
-      <c r="B355" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-GRA-GRN-137</t>
-        </is>
-      </c>
-      <c r="C355" s="26" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D355" s="26" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
-      <c r="E355" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F355" s="25" t="inlineStr">
-        <is>
-          <t>55%</t>
-        </is>
-      </c>
-      <c r="G355" s="25" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="356">
-      <c r="A356" s="25" t="inlineStr">
-        <is>
-          <t>97067</t>
-        </is>
-      </c>
-      <c r="B356" s="26" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="C356" s="26" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
-        </is>
-      </c>
-      <c r="D356" s="26" t="inlineStr">
-        <is>
-          <t>Clackamas</t>
-        </is>
-      </c>
-      <c r="E356" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F356" s="25" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G356" s="25" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="357">
-      <c r="A357" s="25" t="inlineStr">
-        <is>
-          <t>97067</t>
-        </is>
-      </c>
-      <c r="B357" s="26" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="C357" s="26" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
-        </is>
-      </c>
-      <c r="D357" s="26" t="inlineStr">
-        <is>
-          <t>Clackamas</t>
-        </is>
-      </c>
-      <c r="E357" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F357" s="25" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G357" s="25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="358">
-      <c r="A358" s="25" t="inlineStr">
-        <is>
-          <t>97711</t>
-        </is>
-      </c>
-      <c r="B358" s="26" t="inlineStr">
-        <is>
-          <t>NE 15 East</t>
-        </is>
-      </c>
-      <c r="C358" s="26" t="inlineStr">
-        <is>
-          <t>Rowe Creek Complex</t>
-        </is>
-      </c>
-      <c r="D358" s="26" t="inlineStr">
-        <is>
-          <t>Jefferson</t>
-        </is>
-      </c>
-      <c r="E358" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F358" s="25" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G358" s="25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="359">
-      <c r="A359" s="25" t="inlineStr">
-        <is>
-          <t>97442</t>
-        </is>
-      </c>
-      <c r="B359" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-JOS-JCU-302-B</t>
-        </is>
-      </c>
-      <c r="C359" s="26" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D359" s="26" t="inlineStr">
-        <is>
-          <t>Josephine</t>
-        </is>
-      </c>
-      <c r="E359" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F359" s="25" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G359" s="25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="360">
-      <c r="A360" s="25" t="inlineStr">
-        <is>
-          <t>97029</t>
-        </is>
-      </c>
-      <c r="B360" s="26" t="inlineStr">
-        <is>
-          <t>LDWT</t>
-        </is>
-      </c>
-      <c r="C360" s="26" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
-        </is>
-      </c>
-      <c r="D360" s="26" t="inlineStr">
-        <is>
-          <t>Wasco</t>
-        </is>
-      </c>
-      <c r="E360" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F360" s="25" t="inlineStr">
-        <is>
-          <t>1%</t>
-        </is>
-      </c>
-      <c r="G360" s="25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="361">
-      <c r="A361" s="25" t="inlineStr">
-        <is>
-          <t>97029</t>
-        </is>
-      </c>
-      <c r="B361" s="26" t="inlineStr">
-        <is>
-          <t>SBR</t>
-        </is>
-      </c>
-      <c r="C361" s="26" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
-        </is>
-      </c>
-      <c r="D361" s="26" t="inlineStr">
-        <is>
-          <t>Wasco</t>
-        </is>
-      </c>
-      <c r="E361" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F361" s="25" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G361" s="25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="362">
-      <c r="A362" s="25" t="inlineStr">
-        <is>
-          <t>97040</t>
-        </is>
-      </c>
-      <c r="B362" s="26" t="inlineStr">
-        <is>
-          <t>MCR</t>
-        </is>
-      </c>
-      <c r="C362" s="26" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
-        </is>
-      </c>
-      <c r="D362" s="26" t="inlineStr">
-        <is>
-          <t>Wasco</t>
-        </is>
-      </c>
-      <c r="E362" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F362" s="25" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G362" s="25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="363">
-      <c r="A363" s="25" t="inlineStr">
-        <is>
-          <t>97601</t>
-        </is>
-      </c>
-      <c r="B363" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1931</t>
-        </is>
-      </c>
-      <c r="C363" s="26" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D363" s="26" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E363" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F363" s="25" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G363" s="25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="365" ht="60" customHeight="1">
-      <c r="A365" s="27" t="inlineStr">
+    <row r="356" ht="60" customHeight="1">
+      <c r="A356" s="27" t="inlineStr">
         <is>
           <t>Methodology: "% of Zone" = the share of this evac zone's total polygon area that falls within this ZIP's Census ZCTA boundary (area-weighted polygon intersection). "Est. Addresses" = the zone's total AddressesWithin (OEM) × that same area fraction — an area-weighted estimate, not a geocoded address count; assumes uniform address density across the zone polygon. Rows whose estimate rounds below 1 are shown as 1 rather than omitted, since the ZIP is still a real, known intersection for that zone. Source: Oregon OEM Fire_Evacuation_Areas_Public + Census TIGERweb ZCTA.</t>
         </is>
@@ -14893,8 +14578,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A356:G356"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A365:G365"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
